--- a/Practical Task/01_Practical_task.xlsx
+++ b/Practical Task/01_Practical_task.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASDC11\Desktop\Smit\Data_Analytics\PRactical Task\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASDC11\Desktop\Smit\Data_Analytics\Practical Task\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DD9B2595-6C84-4D47-B780-2BBE6F182A43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A66B8F7-DC97-4C8F-8069-3F8929237DF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="5" activeTab="8" xr2:uid="{B7CA3347-B884-4512-82BB-7C62A0B069B5}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="202">
   <si>
     <t>24/01/2026</t>
   </si>
@@ -665,6 +665,9 @@
   </si>
   <si>
     <t>Mohan</t>
+  </si>
+  <si>
+    <t>ss</t>
   </si>
 </sst>
 </file>
@@ -998,18 +1001,6 @@
   </cellStyleXfs>
   <cellXfs count="96">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1043,12 +1034,6 @@
     <xf numFmtId="165" fontId="5" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1062,12 +1047,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1092,15 +1071,6 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1174,9 +1144,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1187,12 +1154,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
@@ -1240,45 +1201,87 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="98">
+  <dxfs count="96">
     <dxf>
       <font>
         <b val="0"/>
@@ -1308,45 +1311,6 @@
           <color rgb="FF3D444D"/>
         </left>
         <right/>
-        <top style="medium">
-          <color rgb="FF3D444D"/>
-        </top>
-        <bottom style="medium">
-          <color rgb="FF3D444D"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color rgb="FFF0F6FC"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="8" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="medium">
-          <color rgb="FF3D444D"/>
-        </left>
-        <right style="medium">
-          <color rgb="FF3D444D"/>
-        </right>
         <top style="medium">
           <color rgb="FF3D444D"/>
         </top>
@@ -1401,13 +1365,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="medium">
-          <color rgb="FF3D444D"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <left style="medium">
           <color rgb="FF3D444D"/>
         </left>
@@ -1430,6 +1387,13 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color rgb="FF3D444D"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -1467,19 +1431,29 @@
       </border>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1512,6 +1486,45 @@
           <color rgb="FF3D444D"/>
         </left>
         <right/>
+        <top style="medium">
+          <color rgb="FF3D444D"/>
+        </top>
+        <bottom style="medium">
+          <color rgb="FF3D444D"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FFF0F6FC"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="8" tint="-0.249977111117893"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="medium">
+          <color rgb="FF3D444D"/>
+        </left>
+        <right style="medium">
+          <color rgb="FF3D444D"/>
+        </right>
         <top style="medium">
           <color rgb="FF3D444D"/>
         </top>
@@ -1566,13 +1579,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="medium">
-          <color rgb="FF3D444D"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <left style="medium">
           <color rgb="FF3D444D"/>
         </left>
@@ -1595,6 +1601,13 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color rgb="FF3D444D"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -1630,33 +1643,6 @@
         <top/>
         <bottom/>
       </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <fill>
@@ -1758,13 +1744,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="medium">
-          <color rgb="FF3D444D"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <left style="medium">
           <color rgb="FF3D444D"/>
         </left>
@@ -1787,6 +1766,13 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color rgb="FF3D444D"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -1825,21 +1811,21 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1926,13 +1912,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="medium">
-          <color rgb="FF3D444D"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <left style="medium">
           <color rgb="FF3D444D"/>
         </left>
@@ -1967,6 +1946,13 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color rgb="FF3D444D"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -2322,13 +2308,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="medium">
-          <color rgb="FF3D444D"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <left style="medium">
           <color rgb="FF3D444D"/>
         </left>
@@ -2367,6 +2346,13 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color rgb="FF3D444D"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -2526,13 +2512,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="medium">
-          <color rgb="FF3D444D"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <left style="medium">
           <color rgb="FF3D444D"/>
         </left>
@@ -2554,6 +2533,13 @@
           <bgColor theme="8" tint="-0.249977111117893"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color rgb="FF3D444D"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -2714,13 +2700,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="medium">
-          <color rgb="FF3D444D"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <left style="medium">
           <color rgb="FF3D444D"/>
         </left>
@@ -2754,6 +2733,13 @@
           <bgColor theme="8" tint="-0.249977111117893"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color rgb="FF3D444D"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -3070,13 +3056,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="medium">
-          <color rgb="FF3D444D"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <left style="medium">
           <color rgb="FF3D444D"/>
         </left>
@@ -3115,6 +3094,13 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color rgb="FF3D444D"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -3258,13 +3244,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="medium">
-          <color rgb="FF3D444D"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <left style="medium">
           <color rgb="FF3D444D"/>
         </left>
@@ -3299,6 +3278,13 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color rgb="FF3D444D"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -3521,13 +3507,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="medium">
-          <color rgb="FF3D444D"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <left style="medium">
           <color rgb="FF3D444D"/>
         </left>
@@ -3566,6 +3545,13 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color rgb="FF3D444D"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -3616,56 +3602,56 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{18DA0779-BBFA-4955-99A8-E0197A43B52B}" name="Table1" displayName="Table1" ref="B4:F24" totalsRowShown="0" headerRowDxfId="97" dataDxfId="96" headerRowBorderDxfId="94" tableBorderDxfId="95" totalsRowBorderDxfId="93">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{18DA0779-BBFA-4955-99A8-E0197A43B52B}" name="Table1" displayName="Table1" ref="B4:F24" totalsRowShown="0" headerRowDxfId="95" dataDxfId="93" headerRowBorderDxfId="94" tableBorderDxfId="92" totalsRowBorderDxfId="91">
   <autoFilter ref="B4:F24" xr:uid="{18DA0779-BBFA-4955-99A8-E0197A43B52B}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{8A0FA5AF-F72E-4C5B-9840-F9FC9FD978B0}" name="Employee ID" dataDxfId="92"/>
-    <tableColumn id="2" xr3:uid="{C66B1B6F-44CA-4E35-B4A3-C13DED973F50}" name="Name" dataDxfId="91"/>
-    <tableColumn id="3" xr3:uid="{EFB23A70-98D8-4625-A5E1-BED0BE5CDEF8}" name="Department" dataDxfId="90"/>
-    <tableColumn id="4" xr3:uid="{9FE7E964-5161-493A-8C0B-7EF47082BC4B}" name="Salary" dataDxfId="89"/>
-    <tableColumn id="5" xr3:uid="{D5DA9CA6-F11B-4203-A797-7C2371C2B251}" name="Joining Date" dataDxfId="88"/>
+    <tableColumn id="1" xr3:uid="{8A0FA5AF-F72E-4C5B-9840-F9FC9FD978B0}" name="Employee ID" dataDxfId="90"/>
+    <tableColumn id="2" xr3:uid="{C66B1B6F-44CA-4E35-B4A3-C13DED973F50}" name="Name" dataDxfId="89"/>
+    <tableColumn id="3" xr3:uid="{EFB23A70-98D8-4625-A5E1-BED0BE5CDEF8}" name="Department" dataDxfId="88"/>
+    <tableColumn id="4" xr3:uid="{9FE7E964-5161-493A-8C0B-7EF47082BC4B}" name="Salary" dataDxfId="87"/>
+    <tableColumn id="5" xr3:uid="{D5DA9CA6-F11B-4203-A797-7C2371C2B251}" name="Joining Date" dataDxfId="86"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{6DE569B0-5193-4D98-AE11-AE12D7F6085B}" name="Table10" displayName="Table10" ref="A5:B10" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15" headerRowBorderDxfId="13" tableBorderDxfId="14" totalsRowBorderDxfId="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{6DE569B0-5193-4D98-AE11-AE12D7F6085B}" name="Table10" displayName="Table10" ref="A5:B10" totalsRowShown="0" headerRowDxfId="6" dataDxfId="4" headerRowBorderDxfId="5" tableBorderDxfId="3" totalsRowBorderDxfId="2">
   <autoFilter ref="A5:B10" xr:uid="{6DE569B0-5193-4D98-AE11-AE12D7F6085B}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{46E193FB-CF97-4AF5-9CCB-771674F6C2F3}" name="Employee Name" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{7171D8FE-54F3-48A0-A358-275EDEA26184}" name="Salary" dataDxfId="10"/>
+    <tableColumn id="1" xr3:uid="{46E193FB-CF97-4AF5-9CCB-771674F6C2F3}" name="Employee Name" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{7171D8FE-54F3-48A0-A358-275EDEA26184}" name="Salary" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{E3E799DC-556D-494B-A4FC-A68F6E63FA4D}" name="Table3" displayName="Table3" ref="B5:E25" totalsRowShown="0" headerRowDxfId="87" dataDxfId="86" headerRowBorderDxfId="84" tableBorderDxfId="85" totalsRowBorderDxfId="83">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{E3E799DC-556D-494B-A4FC-A68F6E63FA4D}" name="Table3" displayName="Table3" ref="B5:E25" totalsRowShown="0" headerRowDxfId="85" dataDxfId="83" headerRowBorderDxfId="84" tableBorderDxfId="82" totalsRowBorderDxfId="81">
   <autoFilter ref="B5:E25" xr:uid="{E3E799DC-556D-494B-A4FC-A68F6E63FA4D}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{A1D4076B-4A58-46C7-915C-5692BA630990}" name="Product Name" dataDxfId="82"/>
-    <tableColumn id="2" xr3:uid="{ED0AE24E-C408-486A-888B-BA05BF205350}" name="Region" dataDxfId="81"/>
-    <tableColumn id="3" xr3:uid="{F7F8E50C-6311-42C6-9A08-DBC6BD163AC1}" name="Sales Amount" dataDxfId="80"/>
-    <tableColumn id="4" xr3:uid="{A5AC8874-28EC-4C4F-A75D-D2014C276156}" name="Salesperson" dataDxfId="79"/>
+    <tableColumn id="1" xr3:uid="{A1D4076B-4A58-46C7-915C-5692BA630990}" name="Product Name" dataDxfId="80"/>
+    <tableColumn id="2" xr3:uid="{ED0AE24E-C408-486A-888B-BA05BF205350}" name="Region" dataDxfId="79"/>
+    <tableColumn id="3" xr3:uid="{F7F8E50C-6311-42C6-9A08-DBC6BD163AC1}" name="Sales Amount" dataDxfId="78"/>
+    <tableColumn id="4" xr3:uid="{A5AC8874-28EC-4C4F-A75D-D2014C276156}" name="Salesperson" dataDxfId="77"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{6353DBD1-4A33-4B9C-92AE-F134AF2B313C}" name="Table4" displayName="Table4" ref="B5:H25" totalsRowShown="0" headerRowDxfId="78" dataDxfId="77" headerRowBorderDxfId="75" tableBorderDxfId="76" totalsRowBorderDxfId="74">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{6353DBD1-4A33-4B9C-92AE-F134AF2B313C}" name="Table4" displayName="Table4" ref="B5:H25" totalsRowShown="0" headerRowDxfId="76" dataDxfId="74" headerRowBorderDxfId="75" tableBorderDxfId="73" totalsRowBorderDxfId="72">
   <autoFilter ref="B5:H25" xr:uid="{6353DBD1-4A33-4B9C-92AE-F134AF2B313C}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{4EC9A07C-F784-4A83-9309-11072C7C5AE3}" name="Roll No" dataDxfId="73"/>
-    <tableColumn id="2" xr3:uid="{15F09AEE-3456-4D81-B47B-6127A88797C6}" name="Student Name" dataDxfId="72"/>
-    <tableColumn id="3" xr3:uid="{34333EFE-8F13-4A6D-8103-0AA3EC869EE2}" name="Maths" dataDxfId="71"/>
-    <tableColumn id="4" xr3:uid="{D8E331F0-5913-4011-97C5-1938C3A26357}" name="Science" dataDxfId="70"/>
-    <tableColumn id="5" xr3:uid="{25CDC323-B080-4A76-B351-E74D6581B90D}" name="English" dataDxfId="69"/>
-    <tableColumn id="7" xr3:uid="{11831898-4099-489D-83C8-A0468D55B891}" name="Total" dataDxfId="68">
+    <tableColumn id="1" xr3:uid="{4EC9A07C-F784-4A83-9309-11072C7C5AE3}" name="Roll No" dataDxfId="71"/>
+    <tableColumn id="2" xr3:uid="{15F09AEE-3456-4D81-B47B-6127A88797C6}" name="Student Name" dataDxfId="70"/>
+    <tableColumn id="3" xr3:uid="{34333EFE-8F13-4A6D-8103-0AA3EC869EE2}" name="Maths" dataDxfId="69"/>
+    <tableColumn id="4" xr3:uid="{D8E331F0-5913-4011-97C5-1938C3A26357}" name="Science" dataDxfId="68"/>
+    <tableColumn id="5" xr3:uid="{25CDC323-B080-4A76-B351-E74D6581B90D}" name="English" dataDxfId="67"/>
+    <tableColumn id="7" xr3:uid="{11831898-4099-489D-83C8-A0468D55B891}" name="Total" dataDxfId="66">
       <calculatedColumnFormula>SUM(Table4[[#This Row],[Maths]:[English]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{3B57DA99-2B54-40FD-A1F3-7ACCA58B86B3}" name="Percentage" dataDxfId="67" dataCellStyle="Percent">
+    <tableColumn id="6" xr3:uid="{3B57DA99-2B54-40FD-A1F3-7ACCA58B86B3}" name="Percentage" dataDxfId="65" dataCellStyle="Percent">
       <calculatedColumnFormula>Table4[[#This Row],[Total]]/300</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3674,43 +3660,43 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{41AE1E97-03ED-48D2-BBAA-A0EEF0591783}" name="Table5" displayName="Table5" ref="B3:D23" totalsRowShown="0" headerRowDxfId="66" dataDxfId="65" headerRowBorderDxfId="63" tableBorderDxfId="64" totalsRowBorderDxfId="62">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{41AE1E97-03ED-48D2-BBAA-A0EEF0591783}" name="Table5" displayName="Table5" ref="B3:D23" totalsRowShown="0" headerRowDxfId="64" dataDxfId="62" headerRowBorderDxfId="63" tableBorderDxfId="61" totalsRowBorderDxfId="60">
   <autoFilter ref="B3:D23" xr:uid="{41AE1E97-03ED-48D2-BBAA-A0EEF0591783}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{DAD03252-6606-42B6-8164-B144BFD80995}" name="Invoice No" dataDxfId="61"/>
-    <tableColumn id="2" xr3:uid="{1CADEC04-EA62-4A04-B5D1-5585CFEE53DD}" name="Date" dataDxfId="60"/>
-    <tableColumn id="3" xr3:uid="{EDB55DE4-ED84-4FA0-9086-5964738F928A}" name="Sales Amount" dataDxfId="59"/>
+    <tableColumn id="1" xr3:uid="{DAD03252-6606-42B6-8164-B144BFD80995}" name="Invoice No" dataDxfId="59"/>
+    <tableColumn id="2" xr3:uid="{1CADEC04-EA62-4A04-B5D1-5585CFEE53DD}" name="Date" dataDxfId="58"/>
+    <tableColumn id="3" xr3:uid="{EDB55DE4-ED84-4FA0-9086-5964738F928A}" name="Sales Amount" dataDxfId="57"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{6B014AC8-3939-4BA6-AAA7-55269CA3410C}" name="Table2" displayName="Table2" ref="A5:C11" totalsRowShown="0" headerRowDxfId="58" dataDxfId="57" headerRowBorderDxfId="55" tableBorderDxfId="56" totalsRowBorderDxfId="54">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{6B014AC8-3939-4BA6-AAA7-55269CA3410C}" name="Table2" displayName="Table2" ref="A5:C11" totalsRowShown="0" headerRowDxfId="56" dataDxfId="54" headerRowBorderDxfId="55" tableBorderDxfId="53" totalsRowBorderDxfId="52">
   <autoFilter ref="A5:C11" xr:uid="{6B014AC8-3939-4BA6-AAA7-55269CA3410C}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{575CD35B-FFB2-4634-956A-53C08A648F35}" name="Employee Name" dataDxfId="53"/>
-    <tableColumn id="2" xr3:uid="{04B512B3-2899-41C1-832F-6FEED5F4B8ED}" name="Department" dataDxfId="52"/>
-    <tableColumn id="3" xr3:uid="{6301DC54-CCAE-44A8-B415-9BA951C56F86}" name="Salary" dataDxfId="51"/>
+    <tableColumn id="1" xr3:uid="{575CD35B-FFB2-4634-956A-53C08A648F35}" name="Employee Name" dataDxfId="51"/>
+    <tableColumn id="2" xr3:uid="{04B512B3-2899-41C1-832F-6FEED5F4B8ED}" name="Department" dataDxfId="50"/>
+    <tableColumn id="3" xr3:uid="{6301DC54-CCAE-44A8-B415-9BA951C56F86}" name="Salary" dataDxfId="49"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{0D466FEE-5CDF-43F9-B141-147938C8B764}" name="Table6" displayName="Table6" ref="A5:H9" totalsRowShown="0" headerRowDxfId="50" dataDxfId="49" headerRowBorderDxfId="47" tableBorderDxfId="48" totalsRowBorderDxfId="46">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{0D466FEE-5CDF-43F9-B141-147938C8B764}" name="Table6" displayName="Table6" ref="A5:H9" totalsRowShown="0" headerRowDxfId="48" dataDxfId="46" headerRowBorderDxfId="47" tableBorderDxfId="45" totalsRowBorderDxfId="44">
   <autoFilter ref="A5:H9" xr:uid="{0D466FEE-5CDF-43F9-B141-147938C8B764}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{C0690093-DC59-4EB4-A109-5665E4F9F0FE}" name="Student Name" dataDxfId="45"/>
-    <tableColumn id="2" xr3:uid="{01B8014F-6EE1-4A38-8D58-7FA55C278CC7}" name="Day 1" dataDxfId="44"/>
-    <tableColumn id="3" xr3:uid="{DA210618-1037-4133-BAA2-275358BB036D}" name="Day 2" dataDxfId="43"/>
-    <tableColumn id="4" xr3:uid="{9B2B916C-C9C2-427C-AD15-82F7D1B8AB03}" name="Day 3" dataDxfId="42"/>
-    <tableColumn id="5" xr3:uid="{99172070-DEDF-4B89-8554-876666226AF8}" name="Day 4" dataDxfId="41"/>
-    <tableColumn id="6" xr3:uid="{D6EB0CE9-F3E2-405F-889F-1F96F9C3A678}" name="Day 5" dataDxfId="40"/>
-    <tableColumn id="7" xr3:uid="{76D2CACB-1CE8-4FC8-8165-E645416F0051}" name="Present" dataDxfId="39">
+    <tableColumn id="1" xr3:uid="{C0690093-DC59-4EB4-A109-5665E4F9F0FE}" name="Student Name" dataDxfId="43"/>
+    <tableColumn id="2" xr3:uid="{01B8014F-6EE1-4A38-8D58-7FA55C278CC7}" name="Day 1" dataDxfId="42"/>
+    <tableColumn id="3" xr3:uid="{DA210618-1037-4133-BAA2-275358BB036D}" name="Day 2" dataDxfId="41"/>
+    <tableColumn id="4" xr3:uid="{9B2B916C-C9C2-427C-AD15-82F7D1B8AB03}" name="Day 3" dataDxfId="40"/>
+    <tableColumn id="5" xr3:uid="{99172070-DEDF-4B89-8554-876666226AF8}" name="Day 4" dataDxfId="39"/>
+    <tableColumn id="6" xr3:uid="{D6EB0CE9-F3E2-405F-889F-1F96F9C3A678}" name="Day 5" dataDxfId="38"/>
+    <tableColumn id="7" xr3:uid="{76D2CACB-1CE8-4FC8-8165-E645416F0051}" name="Present" dataDxfId="37">
       <calculatedColumnFormula>COUNTIF(Table6[[#This Row],[Day 1]:[Day 5]],Table6[[#This Row],[Day 1]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{65B1B56F-E957-4E46-9FBB-C3A46DF71181}" name="Absent" dataDxfId="38">
+    <tableColumn id="8" xr3:uid="{65B1B56F-E957-4E46-9FBB-C3A46DF71181}" name="Absent" dataDxfId="36">
       <calculatedColumnFormula>COUNTIF(Table6[[#This Row],[Day 1]:[Present]],Table6[[#This Row],[Day 2]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3719,34 +3705,34 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{50C93656-7CF0-4C37-8BB6-5DEF1E4B882B}" name="Table7" displayName="Table7" ref="A5:B28" totalsRowShown="0" headerRowDxfId="37" dataDxfId="36" headerRowBorderDxfId="34" tableBorderDxfId="35" totalsRowBorderDxfId="33">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{50C93656-7CF0-4C37-8BB6-5DEF1E4B882B}" name="Table7" displayName="Table7" ref="A5:B28" totalsRowShown="0" headerRowDxfId="35" dataDxfId="33" headerRowBorderDxfId="34" tableBorderDxfId="32" totalsRowBorderDxfId="31">
   <autoFilter ref="A5:B28" xr:uid="{50C93656-7CF0-4C37-8BB6-5DEF1E4B882B}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{E083B74E-2BBD-477E-826A-D77F6966A49B}" name="Order ID" dataDxfId="32"/>
-    <tableColumn id="2" xr3:uid="{BF23E472-95EE-4987-9E06-8822DCEC289C}" name="Sales Amount" dataDxfId="31"/>
+    <tableColumn id="1" xr3:uid="{E083B74E-2BBD-477E-826A-D77F6966A49B}" name="Order ID" dataDxfId="30"/>
+    <tableColumn id="2" xr3:uid="{BF23E472-95EE-4987-9E06-8822DCEC289C}" name="Sales Amount" dataDxfId="29"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{34C50E4F-B9EF-47C5-91F3-0721515A91F2}" name="Table8" displayName="Table8" ref="A5:B10" totalsRowShown="0" headerRowDxfId="28" dataDxfId="27" headerRowBorderDxfId="25" tableBorderDxfId="26" totalsRowBorderDxfId="24">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{34C50E4F-B9EF-47C5-91F3-0721515A91F2}" name="Table8" displayName="Table8" ref="A5:B10" totalsRowShown="0" headerRowDxfId="26" dataDxfId="24" headerRowBorderDxfId="25" tableBorderDxfId="23" totalsRowBorderDxfId="22">
   <autoFilter ref="A5:B10" xr:uid="{34C50E4F-B9EF-47C5-91F3-0721515A91F2}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{2428ABD3-1A1A-44DF-8CED-1AEADAFD460B}" name="Product" dataDxfId="23"/>
-    <tableColumn id="2" xr3:uid="{9A58930C-249A-4833-B37E-DB7380FE3BD1}" name="Sales Amount" dataDxfId="22"/>
+    <tableColumn id="1" xr3:uid="{2428ABD3-1A1A-44DF-8CED-1AEADAFD460B}" name="Product" dataDxfId="21"/>
+    <tableColumn id="2" xr3:uid="{9A58930C-249A-4833-B37E-DB7380FE3BD1}" name="Sales Amount" dataDxfId="20"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{2648F21F-8F0D-4812-A796-63835204CE3D}" name="Table9" displayName="Table9" ref="A5:C10" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6" headerRowBorderDxfId="4" tableBorderDxfId="5" totalsRowBorderDxfId="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{2648F21F-8F0D-4812-A796-63835204CE3D}" name="Table9" displayName="Table9" ref="A5:C10" totalsRowShown="0" headerRowDxfId="17" dataDxfId="15" headerRowBorderDxfId="16" tableBorderDxfId="14" totalsRowBorderDxfId="13">
   <autoFilter ref="A5:C10" xr:uid="{2648F21F-8F0D-4812-A796-63835204CE3D}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{03F7173D-4837-4ADF-8522-CA7A13C37BEF}" name="Roll No" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{08BB40C0-0DEA-42F0-AB7C-27762E038915}" name="Name" dataDxfId="1"/>
-    <tableColumn id="3" xr3:uid="{91131B16-1ACB-4BEA-9EC5-207A1AB69C71}" name="Marks" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{03F7173D-4837-4ADF-8522-CA7A13C37BEF}" name="Roll No" dataDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{08BB40C0-0DEA-42F0-AB7C-27762E038915}" name="Name" dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{91131B16-1ACB-4BEA-9EC5-207A1AB69C71}" name="Marks" dataDxfId="10"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4060,443 +4046,443 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:20" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="78" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
     </row>
     <row r="2" spans="2:20" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="79" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
+      <c r="C2" s="79"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="79"/>
+      <c r="F2" s="79"/>
+      <c r="G2" s="79"/>
+      <c r="H2" s="79"/>
+      <c r="I2" s="79"/>
     </row>
     <row r="3" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="M3" s="3" t="s">
+      <c r="M3" s="80" t="s">
         <v>2</v>
       </c>
-      <c r="N3" s="4"/>
-      <c r="O3" s="4"/>
-      <c r="P3" s="4"/>
-      <c r="Q3" s="4"/>
-      <c r="R3" s="4"/>
-      <c r="S3" s="4"/>
-      <c r="T3" s="4"/>
+      <c r="N3" s="81"/>
+      <c r="O3" s="81"/>
+      <c r="P3" s="81"/>
+      <c r="Q3" s="81"/>
+      <c r="R3" s="81"/>
+      <c r="S3" s="81"/>
+      <c r="T3" s="81"/>
     </row>
     <row r="4" spans="2:20" ht="21" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="4"/>
-      <c r="N4" s="4"/>
-      <c r="O4" s="4"/>
-      <c r="P4" s="4"/>
-      <c r="Q4" s="4"/>
-      <c r="R4" s="4"/>
-      <c r="S4" s="4"/>
-      <c r="T4" s="4"/>
+      <c r="M4" s="81"/>
+      <c r="N4" s="81"/>
+      <c r="O4" s="81"/>
+      <c r="P4" s="81"/>
+      <c r="Q4" s="81"/>
+      <c r="R4" s="81"/>
+      <c r="S4" s="81"/>
+      <c r="T4" s="81"/>
     </row>
     <row r="5" spans="2:20" ht="21" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="10">
+      <c r="E5" s="6">
         <v>32000</v>
       </c>
-      <c r="F5" s="11">
+      <c r="F5" s="7">
         <v>44573</v>
       </c>
-      <c r="M5" s="4"/>
-      <c r="N5" s="4"/>
-      <c r="O5" s="4"/>
-      <c r="P5" s="4"/>
-      <c r="Q5" s="4"/>
-      <c r="R5" s="4"/>
-      <c r="S5" s="4"/>
-      <c r="T5" s="4"/>
+      <c r="M5" s="81"/>
+      <c r="N5" s="81"/>
+      <c r="O5" s="81"/>
+      <c r="P5" s="81"/>
+      <c r="Q5" s="81"/>
+      <c r="R5" s="81"/>
+      <c r="S5" s="81"/>
+      <c r="T5" s="81"/>
     </row>
     <row r="6" spans="2:20" ht="21" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="10">
+      <c r="E6" s="6">
         <v>45000</v>
       </c>
-      <c r="F6" s="12">
+      <c r="F6" s="8">
         <v>44260</v>
       </c>
-      <c r="M6" s="4"/>
-      <c r="N6" s="4"/>
-      <c r="O6" s="4"/>
-      <c r="P6" s="4"/>
-      <c r="Q6" s="4"/>
-      <c r="R6" s="4"/>
-      <c r="S6" s="4"/>
-      <c r="T6" s="4"/>
+      <c r="M6" s="81"/>
+      <c r="N6" s="81"/>
+      <c r="O6" s="81"/>
+      <c r="P6" s="81"/>
+      <c r="Q6" s="81"/>
+      <c r="R6" s="81"/>
+      <c r="S6" s="81"/>
+      <c r="T6" s="81"/>
     </row>
     <row r="7" spans="2:20" ht="21" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="10">
+      <c r="E7" s="6">
         <v>38000</v>
       </c>
-      <c r="F7" s="12">
+      <c r="F7" s="8">
         <v>44030</v>
       </c>
-      <c r="M7" s="4"/>
-      <c r="N7" s="4"/>
-      <c r="O7" s="4"/>
-      <c r="P7" s="4"/>
-      <c r="Q7" s="4"/>
-      <c r="R7" s="4"/>
-      <c r="S7" s="4"/>
-      <c r="T7" s="4"/>
+      <c r="M7" s="81"/>
+      <c r="N7" s="81"/>
+      <c r="O7" s="81"/>
+      <c r="P7" s="81"/>
+      <c r="Q7" s="81"/>
+      <c r="R7" s="81"/>
+      <c r="S7" s="81"/>
+      <c r="T7" s="81"/>
     </row>
     <row r="8" spans="2:20" ht="21" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D8" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E8" s="10">
+      <c r="E8" s="6">
         <v>52000</v>
       </c>
-      <c r="F8" s="12">
+      <c r="F8" s="8">
         <v>43779</v>
       </c>
-      <c r="M8" s="4"/>
-      <c r="N8" s="4"/>
-      <c r="O8" s="4"/>
-      <c r="P8" s="4"/>
-      <c r="Q8" s="4"/>
-      <c r="R8" s="4"/>
-      <c r="S8" s="4"/>
-      <c r="T8" s="4"/>
+      <c r="M8" s="81"/>
+      <c r="N8" s="81"/>
+      <c r="O8" s="81"/>
+      <c r="P8" s="81"/>
+      <c r="Q8" s="81"/>
+      <c r="R8" s="81"/>
+      <c r="S8" s="81"/>
+      <c r="T8" s="81"/>
     </row>
     <row r="9" spans="2:20" ht="21" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C9" s="14" t="s">
+      <c r="C9" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="D9" s="14" t="s">
+      <c r="D9" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="E9" s="15">
+      <c r="E9" s="11">
         <v>30000</v>
       </c>
-      <c r="F9" s="12">
+      <c r="F9" s="8">
         <v>45102</v>
       </c>
-      <c r="M9" s="4"/>
-      <c r="N9" s="4"/>
-      <c r="O9" s="4"/>
-      <c r="P9" s="4"/>
-      <c r="Q9" s="4"/>
-      <c r="R9" s="4"/>
-      <c r="S9" s="4"/>
-      <c r="T9" s="4"/>
+      <c r="M9" s="81"/>
+      <c r="N9" s="81"/>
+      <c r="O9" s="81"/>
+      <c r="P9" s="81"/>
+      <c r="Q9" s="81"/>
+      <c r="R9" s="81"/>
+      <c r="S9" s="81"/>
+      <c r="T9" s="81"/>
     </row>
     <row r="10" spans="2:20" ht="21" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="13" t="s">
+      <c r="B10" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="C10" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="D10" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E10" s="10">
+      <c r="E10" s="6">
         <v>50000</v>
       </c>
-      <c r="F10" s="11">
+      <c r="F10" s="7">
         <v>43565</v>
       </c>
     </row>
     <row r="11" spans="2:20" ht="21" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="D11" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E11" s="10">
+      <c r="E11" s="6">
         <v>75000</v>
       </c>
-      <c r="F11" s="12">
+      <c r="F11" s="8">
         <v>43254</v>
       </c>
     </row>
     <row r="12" spans="2:20" ht="41.25" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="13" t="s">
+      <c r="B12" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="C12" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D12" s="9" t="s">
+      <c r="D12" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E12" s="10">
+      <c r="E12" s="6">
         <v>60000</v>
       </c>
-      <c r="F12" s="12">
+      <c r="F12" s="8">
         <v>44395</v>
       </c>
     </row>
     <row r="13" spans="2:20" ht="21" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C13" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="D13" s="9" t="s">
+      <c r="D13" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="E13" s="10">
+      <c r="E13" s="6">
         <v>25000</v>
       </c>
-      <c r="F13" s="12">
+      <c r="F13" s="8">
         <v>43809</v>
       </c>
     </row>
     <row r="14" spans="2:20" ht="21" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="13" t="s">
+      <c r="B14" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="C14" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="D14" s="9" t="s">
+      <c r="D14" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="E14" s="10">
+      <c r="E14" s="6">
         <v>30000</v>
       </c>
-      <c r="F14" s="12">
+      <c r="F14" s="8">
         <v>45468</v>
       </c>
     </row>
     <row r="15" spans="2:20" ht="21" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B15" s="13" t="s">
+      <c r="B15" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="C15" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="D15" s="9" t="s">
+      <c r="D15" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="E15" s="10">
+      <c r="E15" s="6">
         <v>28000</v>
       </c>
-      <c r="F15" s="11">
+      <c r="F15" s="7">
         <v>42529</v>
       </c>
     </row>
     <row r="16" spans="2:20" ht="21" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="13" t="s">
+      <c r="B16" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="C16" s="9" t="s">
+      <c r="C16" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="D16" s="9" t="s">
+      <c r="D16" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E16" s="10">
+      <c r="E16" s="6">
         <v>35000</v>
       </c>
-      <c r="F16" s="12">
+      <c r="F16" s="8">
         <v>42186</v>
       </c>
     </row>
     <row r="17" spans="2:6" ht="21" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B17" s="13" t="s">
+      <c r="B17" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="C17" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="D17" s="9" t="s">
+      <c r="D17" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="E17" s="10">
+      <c r="E17" s="6">
         <v>40000</v>
       </c>
-      <c r="F17" s="12">
+      <c r="F17" s="8">
         <v>44760</v>
       </c>
     </row>
     <row r="18" spans="2:6" ht="21" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B18" s="13" t="s">
+      <c r="B18" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="C18" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="D18" s="9" t="s">
+      <c r="D18" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E18" s="10">
+      <c r="E18" s="6">
         <v>60000</v>
       </c>
-      <c r="F18" s="12">
+      <c r="F18" s="8">
         <v>43751</v>
       </c>
     </row>
     <row r="19" spans="2:6" ht="21" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B19" s="13" t="s">
+      <c r="B19" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="C19" s="9" t="s">
+      <c r="C19" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="D19" s="9" t="s">
+      <c r="D19" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E19" s="10">
+      <c r="E19" s="6">
         <v>35000</v>
       </c>
-      <c r="F19" s="12">
+      <c r="F19" s="8">
         <v>45833</v>
       </c>
     </row>
     <row r="20" spans="2:6" ht="21" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="13" t="s">
+      <c r="B20" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="C20" s="9" t="s">
+      <c r="C20" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="D20" s="9" t="s">
+      <c r="D20" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="E20" s="10">
+      <c r="E20" s="6">
         <v>15000</v>
       </c>
-      <c r="F20" s="11">
+      <c r="F20" s="7">
         <v>41523</v>
       </c>
     </row>
     <row r="21" spans="2:6" ht="21" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B21" s="13" t="s">
+      <c r="B21" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="C21" s="9" t="s">
+      <c r="C21" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="D21" s="9" t="s">
+      <c r="D21" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E21" s="10">
+      <c r="E21" s="6">
         <v>25000</v>
       </c>
-      <c r="F21" s="12">
+      <c r="F21" s="8">
         <v>40827</v>
       </c>
     </row>
     <row r="22" spans="2:6" ht="21" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B22" s="13" t="s">
+      <c r="B22" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="C22" s="9" t="s">
+      <c r="C22" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="D22" s="9" t="s">
+      <c r="D22" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E22" s="10">
+      <c r="E22" s="6">
         <v>45000</v>
       </c>
-      <c r="F22" s="12">
+      <c r="F22" s="8">
         <v>45125</v>
       </c>
     </row>
     <row r="23" spans="2:6" ht="21" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B23" s="13" t="s">
+      <c r="B23" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="C23" s="9" t="s">
+      <c r="C23" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="D23" s="9" t="s">
+      <c r="D23" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E23" s="10">
+      <c r="E23" s="6">
         <v>55000</v>
       </c>
-      <c r="F23" s="12">
+      <c r="F23" s="8">
         <v>43752</v>
       </c>
     </row>
     <row r="24" spans="2:6" ht="21" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B24" s="13" t="s">
+      <c r="B24" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="C24" s="9" t="s">
+      <c r="C24" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="D24" s="9" t="s">
+      <c r="D24" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E24" s="10">
+      <c r="E24" s="6">
         <v>38000</v>
       </c>
-      <c r="F24" s="12">
+      <c r="F24" s="8">
         <v>46198</v>
       </c>
     </row>
@@ -4523,86 +4509,86 @@
   </cols>
   <sheetData>
     <row r="5" spans="1:12" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="76" t="s">
+      <c r="A5" s="62" t="s">
         <v>133</v>
       </c>
-      <c r="B5" s="78" t="s">
+      <c r="B5" s="64" t="s">
         <v>6</v>
       </c>
-      <c r="J5" s="23" t="s">
+      <c r="J5" s="84" t="s">
         <v>195</v>
       </c>
-      <c r="K5" s="24"/>
-      <c r="L5" s="24"/>
+      <c r="K5" s="85"/>
+      <c r="L5" s="85"/>
     </row>
     <row r="6" spans="1:12" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="79" t="s">
+      <c r="A6" s="65" t="s">
         <v>196</v>
       </c>
-      <c r="B6" s="81">
+      <c r="B6" s="67">
         <v>28000</v>
       </c>
-      <c r="J6" s="24"/>
-      <c r="K6" s="24"/>
-      <c r="L6" s="24"/>
+      <c r="J6" s="85"/>
+      <c r="K6" s="85"/>
+      <c r="L6" s="85"/>
     </row>
     <row r="7" spans="1:12" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="79" t="s">
+      <c r="A7" s="65" t="s">
         <v>197</v>
       </c>
-      <c r="B7" s="81">
+      <c r="B7" s="67">
         <v>34000</v>
       </c>
-      <c r="J7" s="24"/>
-      <c r="K7" s="24"/>
-      <c r="L7" s="24"/>
+      <c r="J7" s="85"/>
+      <c r="K7" s="85"/>
+      <c r="L7" s="85"/>
     </row>
     <row r="8" spans="1:12" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="79" t="s">
+      <c r="A8" s="65" t="s">
         <v>198</v>
       </c>
-      <c r="B8" s="81">
+      <c r="B8" s="67">
         <v>51000</v>
       </c>
-      <c r="J8" s="24"/>
-      <c r="K8" s="24"/>
-      <c r="L8" s="24"/>
+      <c r="J8" s="85"/>
+      <c r="K8" s="85"/>
+      <c r="L8" s="85"/>
     </row>
     <row r="9" spans="1:12" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="79" t="s">
+      <c r="A9" s="65" t="s">
         <v>199</v>
       </c>
-      <c r="B9" s="81">
+      <c r="B9" s="67">
         <v>47000</v>
       </c>
-      <c r="J9" s="24"/>
-      <c r="K9" s="24"/>
-      <c r="L9" s="24"/>
+      <c r="J9" s="85"/>
+      <c r="K9" s="85"/>
+      <c r="L9" s="85"/>
     </row>
     <row r="10" spans="1:12" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A10" s="82" t="s">
+      <c r="A10" s="68" t="s">
         <v>200</v>
       </c>
-      <c r="B10" s="84">
+      <c r="B10" s="70">
         <v>29000</v>
       </c>
-      <c r="J10" s="24"/>
-      <c r="K10" s="24"/>
-      <c r="L10" s="24"/>
+      <c r="J10" s="85"/>
+      <c r="K10" s="85"/>
+      <c r="L10" s="85"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="J5:L10"/>
   </mergeCells>
   <conditionalFormatting sqref="B6:B10">
-    <cfRule type="cellIs" dxfId="17" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="9" priority="1" operator="lessThan">
       <formula>30000</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="2" operator="between">
+    <cfRule type="cellIs" dxfId="8" priority="2" operator="between">
       <formula>30000</formula>
       <formula>49999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="19" priority="3" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="7" priority="3" operator="greaterThanOrEqual">
       <formula>50000</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4625,343 +4611,343 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:21" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="82" t="s">
         <v>52</v>
       </c>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
+      <c r="C1" s="82"/>
+      <c r="D1" s="82"/>
+      <c r="E1" s="82"/>
+      <c r="F1" s="82"/>
     </row>
     <row r="3" spans="2:21" ht="21" x14ac:dyDescent="0.35">
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="83" t="s">
         <v>53</v>
       </c>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-    </row>
-    <row r="5" spans="2:21" s="22" customFormat="1" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="18" t="s">
+      <c r="C3" s="83"/>
+      <c r="D3" s="83"/>
+      <c r="E3" s="83"/>
+    </row>
+    <row r="5" spans="2:21" s="16" customFormat="1" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="D5" s="20" t="s">
+      <c r="D5" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="E5" s="21" t="s">
+      <c r="E5" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="O5" s="23" t="s">
+      <c r="O5" s="84" t="s">
         <v>58</v>
       </c>
-      <c r="P5" s="24"/>
-      <c r="Q5" s="24"/>
-      <c r="R5" s="24"/>
-      <c r="S5" s="24"/>
-      <c r="T5" s="24"/>
-      <c r="U5" s="24"/>
+      <c r="P5" s="85"/>
+      <c r="Q5" s="85"/>
+      <c r="R5" s="85"/>
+      <c r="S5" s="85"/>
+      <c r="T5" s="85"/>
+      <c r="U5" s="85"/>
     </row>
     <row r="6" spans="2:21" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="25" t="s">
+      <c r="B6" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="C6" s="26" t="s">
+      <c r="C6" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="D6" s="27">
+      <c r="D6" s="19">
         <v>45000</v>
       </c>
-      <c r="E6" s="28" t="s">
+      <c r="E6" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="O6" s="24"/>
-      <c r="P6" s="24"/>
-      <c r="Q6" s="24"/>
-      <c r="R6" s="24"/>
-      <c r="S6" s="24"/>
-      <c r="T6" s="24"/>
-      <c r="U6" s="24"/>
+      <c r="O6" s="85"/>
+      <c r="P6" s="85"/>
+      <c r="Q6" s="85"/>
+      <c r="R6" s="85"/>
+      <c r="S6" s="85"/>
+      <c r="T6" s="85"/>
+      <c r="U6" s="85"/>
     </row>
     <row r="7" spans="2:21" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="25" t="s">
+      <c r="B7" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="C7" s="26" t="s">
+      <c r="C7" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="D7" s="27">
+      <c r="D7" s="19">
         <v>1200</v>
       </c>
-      <c r="E7" s="28" t="s">
+      <c r="E7" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="O7" s="24"/>
-      <c r="P7" s="24"/>
-      <c r="Q7" s="24"/>
-      <c r="R7" s="24"/>
-      <c r="S7" s="24"/>
-      <c r="T7" s="24"/>
-      <c r="U7" s="24"/>
+      <c r="O7" s="85"/>
+      <c r="P7" s="85"/>
+      <c r="Q7" s="85"/>
+      <c r="R7" s="85"/>
+      <c r="S7" s="85"/>
+      <c r="T7" s="85"/>
+      <c r="U7" s="85"/>
     </row>
     <row r="8" spans="2:21" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="25" t="s">
+      <c r="B8" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="C8" s="26" t="s">
+      <c r="C8" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="D8" s="27">
+      <c r="D8" s="19">
         <v>18000</v>
       </c>
-      <c r="E8" s="28" t="s">
+      <c r="E8" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="O8" s="24"/>
-      <c r="P8" s="24"/>
-      <c r="Q8" s="24"/>
-      <c r="R8" s="24"/>
-      <c r="S8" s="24"/>
-      <c r="T8" s="24"/>
-      <c r="U8" s="24"/>
+      <c r="O8" s="85"/>
+      <c r="P8" s="85"/>
+      <c r="Q8" s="85"/>
+      <c r="R8" s="85"/>
+      <c r="S8" s="85"/>
+      <c r="T8" s="85"/>
+      <c r="U8" s="85"/>
     </row>
     <row r="9" spans="2:21" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="29" t="s">
+      <c r="B9" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="C9" s="30" t="s">
+      <c r="C9" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="D9" s="31">
+      <c r="D9" s="23">
         <v>62000</v>
       </c>
-      <c r="E9" s="32" t="s">
+      <c r="E9" s="24" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="10" spans="2:21" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="25" t="s">
+      <c r="B10" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="C10" s="26" t="s">
+      <c r="C10" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="D10" s="27">
+      <c r="D10" s="19">
         <v>48500</v>
       </c>
-      <c r="E10" s="28" t="s">
+      <c r="E10" s="20" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="11" spans="2:21" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="25" t="s">
+      <c r="B11" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="C11" s="26" t="s">
+      <c r="C11" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="D11" s="27">
+      <c r="D11" s="19">
         <v>55280</v>
       </c>
-      <c r="E11" s="28" t="s">
+      <c r="E11" s="20" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="12" spans="2:21" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="25" t="s">
+      <c r="B12" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="C12" s="26" t="s">
+      <c r="C12" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="D12" s="27">
+      <c r="D12" s="19">
         <v>62060</v>
       </c>
-      <c r="E12" s="28" t="s">
+      <c r="E12" s="20" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="13" spans="2:21" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="29" t="s">
+      <c r="B13" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="C13" s="30" t="s">
+      <c r="C13" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="D13" s="31">
+      <c r="D13" s="23">
         <v>68840</v>
       </c>
-      <c r="E13" s="32" t="s">
+      <c r="E13" s="24" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="14" spans="2:21" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="25" t="s">
+      <c r="B14" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="C14" s="26" t="s">
+      <c r="C14" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="D14" s="27">
+      <c r="D14" s="19">
         <v>75620</v>
       </c>
-      <c r="E14" s="28" t="s">
+      <c r="E14" s="20" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="15" spans="2:21" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="25" t="s">
+      <c r="B15" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="C15" s="26" t="s">
+      <c r="C15" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="D15" s="27">
+      <c r="D15" s="19">
         <v>82400</v>
       </c>
-      <c r="E15" s="28" t="s">
+      <c r="E15" s="20" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="16" spans="2:21" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="25" t="s">
+      <c r="B16" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="C16" s="26" t="s">
+      <c r="C16" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="D16" s="27">
+      <c r="D16" s="19">
         <v>89180</v>
       </c>
-      <c r="E16" s="28" t="s">
+      <c r="E16" s="20" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="17" spans="2:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="29" t="s">
+      <c r="B17" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="C17" s="30" t="s">
+      <c r="C17" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="D17" s="31">
+      <c r="D17" s="23">
         <v>95960</v>
       </c>
-      <c r="E17" s="32" t="s">
+      <c r="E17" s="24" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="18" spans="2:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="25" t="s">
+      <c r="B18" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="C18" s="26" t="s">
+      <c r="C18" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="D18" s="27">
+      <c r="D18" s="19">
         <v>102740</v>
       </c>
-      <c r="E18" s="28" t="s">
+      <c r="E18" s="20" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="19" spans="2:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="25" t="s">
+      <c r="B19" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="C19" s="26" t="s">
+      <c r="C19" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="D19" s="27">
+      <c r="D19" s="19">
         <v>109520</v>
       </c>
-      <c r="E19" s="28" t="s">
+      <c r="E19" s="20" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="20" spans="2:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="25" t="s">
+      <c r="B20" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="C20" s="26" t="s">
+      <c r="C20" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="D20" s="27">
+      <c r="D20" s="19">
         <v>116300</v>
       </c>
-      <c r="E20" s="28" t="s">
+      <c r="E20" s="20" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="21" spans="2:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="29" t="s">
+      <c r="B21" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="C21" s="30" t="s">
+      <c r="C21" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="D21" s="31">
+      <c r="D21" s="23">
         <v>123080</v>
       </c>
-      <c r="E21" s="32" t="s">
+      <c r="E21" s="24" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="22" spans="2:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="25" t="s">
+      <c r="B22" s="17" t="s">
         <v>74</v>
       </c>
-      <c r="C22" s="26" t="s">
+      <c r="C22" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="D22" s="27">
+      <c r="D22" s="19">
         <v>129860</v>
       </c>
-      <c r="E22" s="28" t="s">
+      <c r="E22" s="20" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="23" spans="2:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="25" t="s">
+      <c r="B23" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="C23" s="26" t="s">
+      <c r="C23" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="D23" s="27">
+      <c r="D23" s="19">
         <v>136640</v>
       </c>
-      <c r="E23" s="28" t="s">
+      <c r="E23" s="20" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="24" spans="2:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="25" t="s">
+      <c r="B24" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="C24" s="26" t="s">
+      <c r="C24" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="D24" s="27">
+      <c r="D24" s="19">
         <v>143420</v>
       </c>
-      <c r="E24" s="28" t="s">
+      <c r="E24" s="20" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="25" spans="2:5" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B25" s="29" t="s">
+      <c r="B25" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="C25" s="30" t="s">
+      <c r="C25" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="D25" s="31">
+      <c r="D25" s="23">
         <v>150200</v>
       </c>
-      <c r="E25" s="32" t="s">
+      <c r="E25" s="24" t="s">
         <v>70</v>
       </c>
     </row>
@@ -4993,589 +4979,589 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:18" ht="21" x14ac:dyDescent="0.35">
-      <c r="B1" s="33" t="s">
+      <c r="B1" s="86" t="s">
         <v>75</v>
       </c>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
+      <c r="C1" s="86"/>
+      <c r="D1" s="86"/>
+      <c r="E1" s="86"/>
+      <c r="F1" s="86"/>
+      <c r="G1" s="86"/>
     </row>
     <row r="3" spans="2:18" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B3" s="34" t="s">
+      <c r="B3" s="87" t="s">
         <v>76</v>
       </c>
-      <c r="C3" s="35"/>
-      <c r="D3" s="35"/>
-      <c r="E3" s="35"/>
-      <c r="F3" s="35"/>
-      <c r="G3" s="35"/>
-      <c r="H3" s="35"/>
+      <c r="C3" s="88"/>
+      <c r="D3" s="88"/>
+      <c r="E3" s="88"/>
+      <c r="F3" s="88"/>
+      <c r="G3" s="88"/>
+      <c r="H3" s="88"/>
     </row>
     <row r="5" spans="2:18" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="36" t="s">
+      <c r="B5" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="C5" s="37" t="s">
+      <c r="C5" s="26" t="s">
         <v>78</v>
       </c>
-      <c r="D5" s="37" t="s">
+      <c r="D5" s="26" t="s">
         <v>79</v>
       </c>
-      <c r="E5" s="37" t="s">
+      <c r="E5" s="26" t="s">
         <v>80</v>
       </c>
-      <c r="F5" s="37" t="s">
+      <c r="F5" s="26" t="s">
         <v>81</v>
       </c>
-      <c r="G5" s="38" t="s">
+      <c r="G5" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="H5" s="39" t="s">
+      <c r="H5" s="28" t="s">
         <v>83</v>
       </c>
-      <c r="M5" s="23" t="s">
+      <c r="M5" s="84" t="s">
         <v>84</v>
       </c>
-      <c r="N5" s="24"/>
-      <c r="O5" s="24"/>
-      <c r="P5" s="24"/>
-      <c r="Q5" s="24"/>
-      <c r="R5" s="24"/>
+      <c r="N5" s="85"/>
+      <c r="O5" s="85"/>
+      <c r="P5" s="85"/>
+      <c r="Q5" s="85"/>
+      <c r="R5" s="85"/>
     </row>
     <row r="6" spans="2:18" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="40">
+      <c r="B6" s="29">
         <v>1</v>
       </c>
-      <c r="C6" s="41" t="s">
+      <c r="C6" s="30" t="s">
         <v>85</v>
       </c>
-      <c r="D6" s="41">
+      <c r="D6" s="30">
         <v>78</v>
       </c>
-      <c r="E6" s="41">
+      <c r="E6" s="30">
         <v>82</v>
       </c>
-      <c r="F6" s="41">
+      <c r="F6" s="30">
         <v>74</v>
       </c>
-      <c r="G6" s="42">
+      <c r="G6" s="31">
         <f>SUM(Table4[[#This Row],[Maths]:[English]])</f>
         <v>234</v>
       </c>
-      <c r="H6" s="43">
+      <c r="H6" s="32">
         <f>Table4[[#This Row],[Total]]/300</f>
         <v>0.78</v>
       </c>
-      <c r="M6" s="24"/>
-      <c r="N6" s="24"/>
-      <c r="O6" s="24"/>
-      <c r="P6" s="24"/>
-      <c r="Q6" s="24"/>
-      <c r="R6" s="24"/>
+      <c r="M6" s="85"/>
+      <c r="N6" s="85"/>
+      <c r="O6" s="85"/>
+      <c r="P6" s="85"/>
+      <c r="Q6" s="85"/>
+      <c r="R6" s="85"/>
     </row>
     <row r="7" spans="2:18" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="40">
+      <c r="B7" s="29">
         <v>2</v>
       </c>
-      <c r="C7" s="41" t="s">
+      <c r="C7" s="30" t="s">
         <v>86</v>
       </c>
-      <c r="D7" s="41">
+      <c r="D7" s="30">
         <v>65</v>
       </c>
-      <c r="E7" s="41">
+      <c r="E7" s="30">
         <v>70</v>
       </c>
-      <c r="F7" s="41">
+      <c r="F7" s="30">
         <v>68</v>
       </c>
-      <c r="G7" s="42">
+      <c r="G7" s="31">
         <f>SUM(Table4[[#This Row],[Maths]:[English]])</f>
         <v>203</v>
       </c>
-      <c r="H7" s="43">
+      <c r="H7" s="32">
         <f>Table4[[#This Row],[Total]]/300</f>
         <v>0.67666666666666664</v>
       </c>
-      <c r="M7" s="24"/>
-      <c r="N7" s="24"/>
-      <c r="O7" s="24"/>
-      <c r="P7" s="24"/>
-      <c r="Q7" s="24"/>
-      <c r="R7" s="24"/>
+      <c r="M7" s="85"/>
+      <c r="N7" s="85"/>
+      <c r="O7" s="85"/>
+      <c r="P7" s="85"/>
+      <c r="Q7" s="85"/>
+      <c r="R7" s="85"/>
     </row>
     <row r="8" spans="2:18" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="40">
+      <c r="B8" s="29">
         <v>3</v>
       </c>
-      <c r="C8" s="41" t="s">
+      <c r="C8" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="D8" s="41">
+      <c r="D8" s="30">
         <v>90</v>
       </c>
-      <c r="E8" s="41">
+      <c r="E8" s="30">
         <v>88</v>
       </c>
-      <c r="F8" s="41">
+      <c r="F8" s="30">
         <v>92</v>
       </c>
-      <c r="G8" s="42">
+      <c r="G8" s="31">
         <f>SUM(Table4[[#This Row],[Maths]:[English]])</f>
         <v>270</v>
       </c>
-      <c r="H8" s="43">
+      <c r="H8" s="32">
         <f>Table4[[#This Row],[Total]]/300</f>
         <v>0.9</v>
       </c>
-      <c r="M8" s="24"/>
-      <c r="N8" s="24"/>
-      <c r="O8" s="24"/>
-      <c r="P8" s="24"/>
-      <c r="Q8" s="24"/>
-      <c r="R8" s="24"/>
+      <c r="M8" s="85"/>
+      <c r="N8" s="85"/>
+      <c r="O8" s="85"/>
+      <c r="P8" s="85"/>
+      <c r="Q8" s="85"/>
+      <c r="R8" s="85"/>
     </row>
     <row r="9" spans="2:18" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="40">
+      <c r="B9" s="29">
         <v>4</v>
       </c>
-      <c r="C9" s="41" t="s">
+      <c r="C9" s="30" t="s">
         <v>88</v>
       </c>
-      <c r="D9" s="41">
+      <c r="D9" s="30">
         <v>35</v>
       </c>
-      <c r="E9" s="41">
+      <c r="E9" s="30">
         <v>40</v>
       </c>
-      <c r="F9" s="41">
+      <c r="F9" s="30">
         <v>38</v>
       </c>
-      <c r="G9" s="42">
+      <c r="G9" s="31">
         <f>SUM(Table4[[#This Row],[Maths]:[English]])</f>
         <v>113</v>
       </c>
-      <c r="H9" s="43">
+      <c r="H9" s="32">
         <f>Table4[[#This Row],[Total]]/300</f>
         <v>0.37666666666666665</v>
       </c>
-      <c r="M9" s="24"/>
-      <c r="N9" s="24"/>
-      <c r="O9" s="24"/>
-      <c r="P9" s="24"/>
-      <c r="Q9" s="24"/>
-      <c r="R9" s="24"/>
+      <c r="M9" s="85"/>
+      <c r="N9" s="85"/>
+      <c r="O9" s="85"/>
+      <c r="P9" s="85"/>
+      <c r="Q9" s="85"/>
+      <c r="R9" s="85"/>
     </row>
     <row r="10" spans="2:18" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="44">
+      <c r="B10" s="33">
         <v>5</v>
       </c>
-      <c r="C10" s="45" t="s">
+      <c r="C10" s="34" t="s">
         <v>89</v>
       </c>
-      <c r="D10" s="45">
+      <c r="D10" s="34">
         <v>55</v>
       </c>
-      <c r="E10" s="45">
+      <c r="E10" s="34">
         <v>60</v>
       </c>
-      <c r="F10" s="45">
+      <c r="F10" s="34">
         <v>58</v>
       </c>
-      <c r="G10" s="46">
+      <c r="G10" s="35">
         <f>SUM(Table4[[#This Row],[Maths]:[English]])</f>
         <v>173</v>
       </c>
-      <c r="H10" s="47">
+      <c r="H10" s="36">
         <f>Table4[[#This Row],[Total]]/300</f>
         <v>0.57666666666666666</v>
       </c>
-      <c r="M10" s="24"/>
-      <c r="N10" s="24"/>
-      <c r="O10" s="24"/>
-      <c r="P10" s="24"/>
-      <c r="Q10" s="24"/>
-      <c r="R10" s="24"/>
+      <c r="M10" s="85"/>
+      <c r="N10" s="85"/>
+      <c r="O10" s="85"/>
+      <c r="P10" s="85"/>
+      <c r="Q10" s="85"/>
+      <c r="R10" s="85"/>
     </row>
     <row r="11" spans="2:18" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="40">
+      <c r="B11" s="29">
         <v>6</v>
       </c>
-      <c r="C11" s="41" t="s">
+      <c r="C11" s="30" t="s">
         <v>90</v>
       </c>
-      <c r="D11" s="41">
+      <c r="D11" s="30">
         <v>82</v>
       </c>
-      <c r="E11" s="41">
+      <c r="E11" s="30">
         <v>44</v>
       </c>
-      <c r="F11" s="41">
+      <c r="F11" s="30">
         <v>78</v>
       </c>
-      <c r="G11" s="42">
+      <c r="G11" s="31">
         <f>SUM(Table4[[#This Row],[Maths]:[English]])</f>
         <v>204</v>
       </c>
-      <c r="H11" s="43">
+      <c r="H11" s="32">
         <f>Table4[[#This Row],[Total]]/300</f>
         <v>0.68</v>
       </c>
-      <c r="M11" s="24"/>
-      <c r="N11" s="24"/>
-      <c r="O11" s="24"/>
-      <c r="P11" s="24"/>
-      <c r="Q11" s="24"/>
-      <c r="R11" s="24"/>
+      <c r="M11" s="85"/>
+      <c r="N11" s="85"/>
+      <c r="O11" s="85"/>
+      <c r="P11" s="85"/>
+      <c r="Q11" s="85"/>
+      <c r="R11" s="85"/>
     </row>
     <row r="12" spans="2:18" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="40">
+      <c r="B12" s="29">
         <v>7</v>
       </c>
-      <c r="C12" s="41" t="s">
+      <c r="C12" s="30" t="s">
         <v>91</v>
       </c>
-      <c r="D12" s="41">
+      <c r="D12" s="30">
         <v>70</v>
       </c>
-      <c r="E12" s="41">
+      <c r="E12" s="30">
         <v>58</v>
       </c>
-      <c r="F12" s="41">
+      <c r="F12" s="30">
         <v>65</v>
       </c>
-      <c r="G12" s="42">
+      <c r="G12" s="31">
         <f>SUM(Table4[[#This Row],[Maths]:[English]])</f>
         <v>193</v>
       </c>
-      <c r="H12" s="43">
+      <c r="H12" s="32">
         <f>Table4[[#This Row],[Total]]/300</f>
         <v>0.64333333333333331</v>
       </c>
     </row>
     <row r="13" spans="2:18" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="40">
+      <c r="B13" s="29">
         <v>8</v>
       </c>
-      <c r="C13" s="41" t="s">
+      <c r="C13" s="30" t="s">
         <v>92</v>
       </c>
-      <c r="D13" s="41">
+      <c r="D13" s="30">
         <v>88</v>
       </c>
-      <c r="E13" s="41">
+      <c r="E13" s="30">
         <v>36</v>
       </c>
-      <c r="F13" s="41">
+      <c r="F13" s="30">
         <v>48</v>
       </c>
-      <c r="G13" s="42">
+      <c r="G13" s="31">
         <f>SUM(Table4[[#This Row],[Maths]:[English]])</f>
         <v>172</v>
       </c>
-      <c r="H13" s="43">
+      <c r="H13" s="32">
         <f>Table4[[#This Row],[Total]]/300</f>
         <v>0.57333333333333336</v>
       </c>
     </row>
     <row r="14" spans="2:18" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="40">
+      <c r="B14" s="29">
         <v>9</v>
       </c>
-      <c r="C14" s="41" t="s">
+      <c r="C14" s="30" t="s">
         <v>93</v>
       </c>
-      <c r="D14" s="41">
+      <c r="D14" s="30">
         <v>40</v>
       </c>
-      <c r="E14" s="41">
+      <c r="E14" s="30">
         <v>88</v>
       </c>
-      <c r="F14" s="41">
+      <c r="F14" s="30">
         <v>37</v>
       </c>
-      <c r="G14" s="42">
+      <c r="G14" s="31">
         <f>SUM(Table4[[#This Row],[Maths]:[English]])</f>
         <v>165</v>
       </c>
-      <c r="H14" s="43">
+      <c r="H14" s="32">
         <f>Table4[[#This Row],[Total]]/300</f>
         <v>0.55000000000000004</v>
       </c>
     </row>
     <row r="15" spans="2:18" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="44">
+      <c r="B15" s="33">
         <v>10</v>
       </c>
-      <c r="C15" s="41" t="s">
+      <c r="C15" s="30" t="s">
         <v>94</v>
       </c>
-      <c r="D15" s="45">
+      <c r="D15" s="34">
         <v>60</v>
       </c>
-      <c r="E15" s="41">
+      <c r="E15" s="30">
         <v>45</v>
       </c>
-      <c r="F15" s="41">
+      <c r="F15" s="30">
         <v>68</v>
       </c>
-      <c r="G15" s="42">
+      <c r="G15" s="31">
         <f>SUM(Table4[[#This Row],[Maths]:[English]])</f>
         <v>173</v>
       </c>
-      <c r="H15" s="43">
+      <c r="H15" s="32">
         <f>Table4[[#This Row],[Total]]/300</f>
         <v>0.57666666666666666</v>
       </c>
     </row>
     <row r="16" spans="2:18" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="40">
+      <c r="B16" s="29">
         <v>11</v>
       </c>
-      <c r="C16" s="41" t="s">
+      <c r="C16" s="30" t="s">
         <v>95</v>
       </c>
-      <c r="D16" s="41">
+      <c r="D16" s="30">
         <v>74</v>
       </c>
-      <c r="E16" s="41">
+      <c r="E16" s="30">
         <v>70</v>
       </c>
-      <c r="F16" s="41">
+      <c r="F16" s="30">
         <v>59</v>
       </c>
-      <c r="G16" s="42">
+      <c r="G16" s="31">
         <f>SUM(Table4[[#This Row],[Maths]:[English]])</f>
         <v>203</v>
       </c>
-      <c r="H16" s="43">
+      <c r="H16" s="32">
         <f>Table4[[#This Row],[Total]]/300</f>
         <v>0.67666666666666664</v>
       </c>
     </row>
     <row r="17" spans="2:8" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="40">
+      <c r="B17" s="29">
         <v>12</v>
       </c>
-      <c r="C17" s="41" t="s">
+      <c r="C17" s="30" t="s">
         <v>96</v>
       </c>
-      <c r="D17" s="41">
+      <c r="D17" s="30">
         <v>68</v>
       </c>
-      <c r="E17" s="41">
+      <c r="E17" s="30">
         <v>60</v>
       </c>
-      <c r="F17" s="41">
+      <c r="F17" s="30">
         <v>48</v>
       </c>
-      <c r="G17" s="42">
+      <c r="G17" s="31">
         <f>SUM(Table4[[#This Row],[Maths]:[English]])</f>
         <v>176</v>
       </c>
-      <c r="H17" s="43">
+      <c r="H17" s="32">
         <f>Table4[[#This Row],[Total]]/300</f>
         <v>0.58666666666666667</v>
       </c>
     </row>
     <row r="18" spans="2:8" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="40">
+      <c r="B18" s="29">
         <v>13</v>
       </c>
-      <c r="C18" s="41" t="s">
+      <c r="C18" s="30" t="s">
         <v>97</v>
       </c>
-      <c r="D18" s="41">
+      <c r="D18" s="30">
         <v>92</v>
       </c>
-      <c r="E18" s="41">
+      <c r="E18" s="30">
         <v>25</v>
       </c>
-      <c r="F18" s="41">
+      <c r="F18" s="30">
         <v>90</v>
       </c>
-      <c r="G18" s="42">
+      <c r="G18" s="31">
         <f>SUM(Table4[[#This Row],[Maths]:[English]])</f>
         <v>207</v>
       </c>
-      <c r="H18" s="43">
+      <c r="H18" s="32">
         <f>Table4[[#This Row],[Total]]/300</f>
         <v>0.69</v>
       </c>
     </row>
     <row r="19" spans="2:8" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="40">
+      <c r="B19" s="29">
         <v>14</v>
       </c>
-      <c r="C19" s="41" t="s">
+      <c r="C19" s="30" t="s">
         <v>98</v>
       </c>
-      <c r="D19" s="41">
+      <c r="D19" s="30">
         <v>38</v>
       </c>
-      <c r="E19" s="41">
+      <c r="E19" s="30">
         <v>39</v>
       </c>
-      <c r="F19" s="41">
+      <c r="F19" s="30">
         <v>45</v>
       </c>
-      <c r="G19" s="42">
+      <c r="G19" s="31">
         <f>SUM(Table4[[#This Row],[Maths]:[English]])</f>
         <v>122</v>
       </c>
-      <c r="H19" s="43">
+      <c r="H19" s="32">
         <f>Table4[[#This Row],[Total]]/300</f>
         <v>0.40666666666666668</v>
       </c>
     </row>
     <row r="20" spans="2:8" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="44">
+      <c r="B20" s="33">
         <v>15</v>
       </c>
-      <c r="C20" s="41" t="s">
+      <c r="C20" s="30" t="s">
         <v>99</v>
       </c>
-      <c r="D20" s="45">
+      <c r="D20" s="34">
         <v>58</v>
       </c>
-      <c r="E20" s="41">
+      <c r="E20" s="30">
         <v>55</v>
       </c>
-      <c r="F20" s="41">
+      <c r="F20" s="30">
         <v>88</v>
       </c>
-      <c r="G20" s="42">
+      <c r="G20" s="31">
         <f>SUM(Table4[[#This Row],[Maths]:[English]])</f>
         <v>201</v>
       </c>
-      <c r="H20" s="43">
+      <c r="H20" s="32">
         <f>Table4[[#This Row],[Total]]/300</f>
         <v>0.67</v>
       </c>
     </row>
     <row r="21" spans="2:8" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="40">
+      <c r="B21" s="29">
         <v>16</v>
       </c>
-      <c r="C21" s="41" t="s">
+      <c r="C21" s="30" t="s">
         <v>100</v>
       </c>
-      <c r="D21" s="41">
+      <c r="D21" s="30">
         <v>78</v>
       </c>
-      <c r="E21" s="41">
+      <c r="E21" s="30">
         <v>84</v>
       </c>
-      <c r="F21" s="41">
+      <c r="F21" s="30">
         <v>90</v>
       </c>
-      <c r="G21" s="42">
+      <c r="G21" s="31">
         <f>SUM(Table4[[#This Row],[Maths]:[English]])</f>
         <v>252</v>
       </c>
-      <c r="H21" s="43">
+      <c r="H21" s="32">
         <f>Table4[[#This Row],[Total]]/300</f>
         <v>0.84</v>
       </c>
     </row>
     <row r="22" spans="2:8" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="40">
+      <c r="B22" s="29">
         <v>17</v>
       </c>
-      <c r="C22" s="41" t="s">
+      <c r="C22" s="30" t="s">
         <v>101</v>
       </c>
-      <c r="D22" s="41">
+      <c r="D22" s="30">
         <v>65</v>
       </c>
-      <c r="E22" s="41">
+      <c r="E22" s="30">
         <v>90</v>
       </c>
-      <c r="F22" s="41">
+      <c r="F22" s="30">
         <v>95</v>
       </c>
-      <c r="G22" s="42">
+      <c r="G22" s="31">
         <f>SUM(Table4[[#This Row],[Maths]:[English]])</f>
         <v>250</v>
       </c>
-      <c r="H22" s="43">
+      <c r="H22" s="32">
         <f>Table4[[#This Row],[Total]]/300</f>
         <v>0.83333333333333337</v>
       </c>
     </row>
     <row r="23" spans="2:8" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="40">
+      <c r="B23" s="29">
         <v>18</v>
       </c>
-      <c r="C23" s="41" t="s">
+      <c r="C23" s="30" t="s">
         <v>102</v>
       </c>
-      <c r="D23" s="41">
+      <c r="D23" s="30">
         <v>90</v>
       </c>
-      <c r="E23" s="41">
+      <c r="E23" s="30">
         <v>78</v>
       </c>
-      <c r="F23" s="41">
+      <c r="F23" s="30">
         <v>45</v>
       </c>
-      <c r="G23" s="42">
+      <c r="G23" s="31">
         <f>SUM(Table4[[#This Row],[Maths]:[English]])</f>
         <v>213</v>
       </c>
-      <c r="H23" s="43">
+      <c r="H23" s="32">
         <f>Table4[[#This Row],[Total]]/300</f>
         <v>0.71</v>
       </c>
     </row>
     <row r="24" spans="2:8" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="40">
+      <c r="B24" s="29">
         <v>19</v>
       </c>
-      <c r="C24" s="41" t="s">
+      <c r="C24" s="30" t="s">
         <v>103</v>
       </c>
-      <c r="D24" s="41">
+      <c r="D24" s="30">
         <v>35</v>
       </c>
-      <c r="E24" s="41">
+      <c r="E24" s="30">
         <v>63</v>
       </c>
-      <c r="F24" s="41">
+      <c r="F24" s="30">
         <v>76</v>
       </c>
-      <c r="G24" s="42">
+      <c r="G24" s="31">
         <f>SUM(Table4[[#This Row],[Maths]:[English]])</f>
         <v>174</v>
       </c>
-      <c r="H24" s="43">
+      <c r="H24" s="32">
         <f>Table4[[#This Row],[Total]]/300</f>
         <v>0.57999999999999996</v>
       </c>
     </row>
     <row r="25" spans="2:8" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="44">
+      <c r="B25" s="33">
         <v>20</v>
       </c>
-      <c r="C25" s="41" t="s">
+      <c r="C25" s="30" t="s">
         <v>104</v>
       </c>
-      <c r="D25" s="45">
+      <c r="D25" s="34">
         <v>55</v>
       </c>
-      <c r="E25" s="41">
+      <c r="E25" s="30">
         <v>85</v>
       </c>
-      <c r="F25" s="41">
+      <c r="F25" s="30">
         <v>66</v>
       </c>
-      <c r="G25" s="42">
+      <c r="G25" s="31">
         <f>SUM(Table4[[#This Row],[Maths]:[English]])</f>
         <v>206</v>
       </c>
-      <c r="H25" s="43">
+      <c r="H25" s="32">
         <f>Table4[[#This Row],[Total]]/300</f>
         <v>0.68666666666666665</v>
       </c>
@@ -5604,299 +5590,299 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:16" ht="21" x14ac:dyDescent="0.35">
-      <c r="B1" s="33" t="s">
+      <c r="B1" s="86" t="s">
         <v>105</v>
       </c>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
+      <c r="C1" s="86"/>
+      <c r="D1" s="86"/>
+      <c r="E1" s="86"/>
+      <c r="F1" s="86"/>
     </row>
     <row r="3" spans="2:16" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="48" t="s">
+      <c r="B3" s="37" t="s">
         <v>106</v>
       </c>
-      <c r="C3" s="49" t="s">
+      <c r="C3" s="38" t="s">
         <v>107</v>
       </c>
-      <c r="D3" s="50" t="s">
+      <c r="D3" s="39" t="s">
         <v>56</v>
       </c>
-      <c r="M3" s="23" t="s">
+      <c r="M3" s="84" t="s">
         <v>108</v>
       </c>
-      <c r="N3" s="24"/>
-      <c r="O3" s="24"/>
-      <c r="P3" s="24"/>
+      <c r="N3" s="85"/>
+      <c r="O3" s="85"/>
+      <c r="P3" s="85"/>
     </row>
     <row r="4" spans="2:16" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="51" t="s">
+      <c r="B4" s="40" t="s">
         <v>109</v>
       </c>
-      <c r="C4" s="52">
+      <c r="C4" s="41">
         <v>45292</v>
       </c>
-      <c r="D4" s="53">
+      <c r="D4" s="42">
         <v>12000</v>
       </c>
-      <c r="M4" s="24"/>
-      <c r="N4" s="24"/>
-      <c r="O4" s="24"/>
-      <c r="P4" s="24"/>
+      <c r="M4" s="85"/>
+      <c r="N4" s="85"/>
+      <c r="O4" s="85"/>
+      <c r="P4" s="85"/>
     </row>
     <row r="5" spans="2:16" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="51" t="s">
+      <c r="B5" s="40" t="s">
         <v>110</v>
       </c>
-      <c r="C5" s="52">
+      <c r="C5" s="41">
         <v>45293</v>
       </c>
-      <c r="D5" s="53">
+      <c r="D5" s="42">
         <v>25000</v>
       </c>
-      <c r="M5" s="24"/>
-      <c r="N5" s="24"/>
-      <c r="O5" s="24"/>
-      <c r="P5" s="24"/>
+      <c r="M5" s="85"/>
+      <c r="N5" s="85"/>
+      <c r="O5" s="85"/>
+      <c r="P5" s="85"/>
     </row>
     <row r="6" spans="2:16" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="51" t="s">
+      <c r="B6" s="40" t="s">
         <v>111</v>
       </c>
-      <c r="C6" s="52">
+      <c r="C6" s="41">
         <v>45294</v>
       </c>
-      <c r="D6" s="53">
+      <c r="D6" s="42">
         <v>8000</v>
       </c>
-      <c r="M6" s="24"/>
-      <c r="N6" s="24"/>
-      <c r="O6" s="24"/>
-      <c r="P6" s="24"/>
+      <c r="M6" s="85"/>
+      <c r="N6" s="85"/>
+      <c r="O6" s="85"/>
+      <c r="P6" s="85"/>
     </row>
     <row r="7" spans="2:16" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="51" t="s">
+      <c r="B7" s="40" t="s">
         <v>112</v>
       </c>
-      <c r="C7" s="52">
+      <c r="C7" s="41">
         <v>45295</v>
       </c>
-      <c r="D7" s="53">
+      <c r="D7" s="42">
         <v>32000</v>
       </c>
-      <c r="M7" s="24"/>
-      <c r="N7" s="24"/>
-      <c r="O7" s="24"/>
-      <c r="P7" s="24"/>
+      <c r="M7" s="85"/>
+      <c r="N7" s="85"/>
+      <c r="O7" s="85"/>
+      <c r="P7" s="85"/>
     </row>
     <row r="8" spans="2:16" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="54" t="s">
+      <c r="B8" s="43" t="s">
         <v>113</v>
       </c>
-      <c r="C8" s="52">
+      <c r="C8" s="41">
         <v>45296</v>
       </c>
-      <c r="D8" s="55">
+      <c r="D8" s="44">
         <v>15000</v>
       </c>
     </row>
     <row r="9" spans="2:16" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="51" t="s">
+      <c r="B9" s="40" t="s">
         <v>114</v>
       </c>
-      <c r="C9" s="52">
+      <c r="C9" s="41">
         <v>45515</v>
       </c>
-      <c r="D9" s="53">
+      <c r="D9" s="42">
         <v>20000</v>
       </c>
     </row>
     <row r="10" spans="2:16" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="51" t="s">
+      <c r="B10" s="40" t="s">
         <v>115</v>
       </c>
-      <c r="C10" s="52">
+      <c r="C10" s="41">
         <v>45513</v>
       </c>
-      <c r="D10" s="53">
+      <c r="D10" s="42">
         <v>20000</v>
       </c>
     </row>
     <row r="11" spans="2:16" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="51" t="s">
+      <c r="B11" s="40" t="s">
         <v>116</v>
       </c>
-      <c r="C11" s="52">
+      <c r="C11" s="41">
         <v>45584</v>
       </c>
-      <c r="D11" s="53">
+      <c r="D11" s="42">
         <v>15000</v>
       </c>
     </row>
     <row r="12" spans="2:16" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="51" t="s">
+      <c r="B12" s="40" t="s">
         <v>117</v>
       </c>
-      <c r="C12" s="52">
+      <c r="C12" s="41">
         <v>45447</v>
       </c>
-      <c r="D12" s="53">
+      <c r="D12" s="42">
         <v>22000</v>
       </c>
     </row>
     <row r="13" spans="2:16" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="54" t="s">
+      <c r="B13" s="43" t="s">
         <v>118</v>
       </c>
-      <c r="C13" s="52">
+      <c r="C13" s="41">
         <v>45648</v>
       </c>
-      <c r="D13" s="53">
+      <c r="D13" s="42">
         <v>13000</v>
       </c>
     </row>
     <row r="14" spans="2:16" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="51" t="s">
+      <c r="B14" s="40" t="s">
         <v>119</v>
       </c>
-      <c r="C14" s="52">
+      <c r="C14" s="41">
         <v>45455</v>
       </c>
-      <c r="D14" s="53">
+      <c r="D14" s="42">
         <v>10000</v>
       </c>
     </row>
     <row r="15" spans="2:16" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="51" t="s">
+      <c r="B15" s="40" t="s">
         <v>120</v>
       </c>
-      <c r="C15" s="52">
+      <c r="C15" s="41">
         <v>45327</v>
       </c>
-      <c r="D15" s="53">
+      <c r="D15" s="42">
         <v>4000</v>
       </c>
     </row>
     <row r="16" spans="2:16" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="51" t="s">
+      <c r="B16" s="40" t="s">
         <v>121</v>
       </c>
-      <c r="C16" s="52">
+      <c r="C16" s="41">
         <v>45334</v>
       </c>
-      <c r="D16" s="53">
+      <c r="D16" s="42">
         <v>12000</v>
       </c>
     </row>
     <row r="17" spans="2:4" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="51" t="s">
+      <c r="B17" s="40" t="s">
         <v>122</v>
       </c>
-      <c r="C17" s="52">
+      <c r="C17" s="41">
         <v>45369</v>
       </c>
-      <c r="D17" s="53">
+      <c r="D17" s="42">
         <v>3000</v>
       </c>
     </row>
     <row r="18" spans="2:4" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="54" t="s">
+      <c r="B18" s="43" t="s">
         <v>123</v>
       </c>
-      <c r="C18" s="52">
+      <c r="C18" s="41">
         <v>45644</v>
       </c>
-      <c r="D18" s="53">
+      <c r="D18" s="42">
         <v>5000</v>
       </c>
     </row>
     <row r="19" spans="2:4" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="51" t="s">
+      <c r="B19" s="40" t="s">
         <v>124</v>
       </c>
-      <c r="C19" s="52">
+      <c r="C19" s="41">
         <v>45509</v>
       </c>
-      <c r="D19" s="53">
+      <c r="D19" s="42">
         <v>8000</v>
       </c>
     </row>
     <row r="20" spans="2:4" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="51" t="s">
+      <c r="B20" s="40" t="s">
         <v>125</v>
       </c>
-      <c r="C20" s="52">
+      <c r="C20" s="41">
         <v>45595</v>
       </c>
-      <c r="D20" s="53">
+      <c r="D20" s="42">
         <v>11000</v>
       </c>
     </row>
     <row r="21" spans="2:4" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="51" t="s">
+      <c r="B21" s="40" t="s">
         <v>126</v>
       </c>
-      <c r="C21" s="52">
+      <c r="C21" s="41">
         <v>45458</v>
       </c>
-      <c r="D21" s="53">
+      <c r="D21" s="42">
         <v>12000</v>
       </c>
     </row>
     <row r="22" spans="2:4" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="51" t="s">
+      <c r="B22" s="40" t="s">
         <v>127</v>
       </c>
-      <c r="C22" s="52">
+      <c r="C22" s="41">
         <v>45509</v>
       </c>
-      <c r="D22" s="53">
+      <c r="D22" s="42">
         <v>3000</v>
       </c>
     </row>
     <row r="23" spans="2:4" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="54" t="s">
+      <c r="B23" s="43" t="s">
         <v>128</v>
       </c>
-      <c r="C23" s="52">
+      <c r="C23" s="41">
         <v>45625</v>
       </c>
-      <c r="D23" s="53">
+      <c r="D23" s="42">
         <v>16000</v>
       </c>
     </row>
     <row r="25" spans="2:4" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="C25" s="56" t="s">
+      <c r="C25" s="45" t="s">
         <v>129</v>
       </c>
-      <c r="D25" s="57">
+      <c r="D25" s="46">
         <f>SUM(Table5[Sales Amount])</f>
         <v>266000</v>
       </c>
     </row>
     <row r="27" spans="2:4" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="C27" s="58" t="s">
+      <c r="C27" s="47" t="s">
         <v>130</v>
       </c>
-      <c r="D27" s="59">
+      <c r="D27" s="48">
         <f>AVERAGE(Table5[Sales Amount])</f>
         <v>13300</v>
       </c>
     </row>
     <row r="29" spans="2:4" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="C29" s="60" t="s">
+      <c r="C29" s="49" t="s">
         <v>131</v>
       </c>
-      <c r="D29" s="60">
+      <c r="D29" s="49">
         <f>MAX(Table5[Sales Amount])</f>
         <v>32000</v>
       </c>
     </row>
     <row r="30" spans="2:4" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="C30" s="60" t="s">
+      <c r="C30" s="49" t="s">
         <v>132</v>
       </c>
-      <c r="D30" s="60">
+      <c r="D30" s="49">
         <f>MIN(Table5[Sales Amount])</f>
         <v>3000</v>
       </c>
@@ -5924,151 +5910,151 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B1" s="61"/>
-      <c r="C1" s="61"/>
-      <c r="D1" s="61"/>
-      <c r="E1" s="61"/>
-    </row>
-    <row r="5" spans="1:14" s="65" customFormat="1" ht="41.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="62" t="s">
+      <c r="B1" s="89"/>
+      <c r="C1" s="89"/>
+      <c r="D1" s="89"/>
+      <c r="E1" s="89"/>
+    </row>
+    <row r="5" spans="1:14" s="53" customFormat="1" ht="41.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="50" t="s">
         <v>133</v>
       </c>
-      <c r="B5" s="63" t="s">
+      <c r="B5" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="64" t="s">
+      <c r="C5" s="52" t="s">
         <v>6</v>
       </c>
-      <c r="J5" s="66" t="s">
+      <c r="J5" s="90" t="s">
         <v>134</v>
       </c>
-      <c r="K5" s="67"/>
-      <c r="L5" s="67"/>
-      <c r="M5" s="67"/>
-      <c r="N5" s="67"/>
+      <c r="K5" s="91"/>
+      <c r="L5" s="91"/>
+      <c r="M5" s="91"/>
+      <c r="N5" s="91"/>
     </row>
     <row r="6" spans="1:14" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="68" t="s">
+      <c r="A6" s="54" t="s">
         <v>135</v>
       </c>
-      <c r="B6" s="69" t="s">
+      <c r="B6" s="55" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="70">
+      <c r="C6" s="56">
         <v>28000</v>
       </c>
-      <c r="J6" s="67"/>
-      <c r="K6" s="67"/>
-      <c r="L6" s="67"/>
-      <c r="M6" s="67"/>
-      <c r="N6" s="67"/>
+      <c r="J6" s="91"/>
+      <c r="K6" s="91"/>
+      <c r="L6" s="91"/>
+      <c r="M6" s="91"/>
+      <c r="N6" s="91"/>
     </row>
     <row r="7" spans="1:14" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="68" t="s">
+      <c r="A7" s="54" t="s">
         <v>136</v>
       </c>
-      <c r="B7" s="69" t="s">
+      <c r="B7" s="55" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="70">
+      <c r="C7" s="56">
         <v>45000</v>
       </c>
-      <c r="J7" s="67"/>
-      <c r="K7" s="67"/>
-      <c r="L7" s="67"/>
-      <c r="M7" s="67"/>
-      <c r="N7" s="67"/>
+      <c r="J7" s="91"/>
+      <c r="K7" s="91"/>
+      <c r="L7" s="91"/>
+      <c r="M7" s="91"/>
+      <c r="N7" s="91"/>
     </row>
     <row r="8" spans="1:14" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="68" t="s">
+      <c r="A8" s="54" t="s">
         <v>137</v>
       </c>
-      <c r="B8" s="69" t="s">
+      <c r="B8" s="55" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="70">
+      <c r="C8" s="56">
         <v>50000</v>
       </c>
-      <c r="J8" s="67"/>
-      <c r="K8" s="67"/>
-      <c r="L8" s="67"/>
-      <c r="M8" s="67"/>
-      <c r="N8" s="67"/>
+      <c r="J8" s="91"/>
+      <c r="K8" s="91"/>
+      <c r="L8" s="91"/>
+      <c r="M8" s="91"/>
+      <c r="N8" s="91"/>
     </row>
     <row r="9" spans="1:14" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="68" t="s">
+      <c r="A9" s="54" t="s">
         <v>138</v>
       </c>
-      <c r="B9" s="69" t="s">
+      <c r="B9" s="55" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="70">
+      <c r="C9" s="56">
         <v>42000</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="68" t="s">
+      <c r="A10" s="54" t="s">
         <v>139</v>
       </c>
-      <c r="B10" s="69" t="s">
+      <c r="B10" s="55" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="70">
+      <c r="C10" s="56">
         <v>30000</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A11" s="71" t="s">
+      <c r="A11" s="57" t="s">
         <v>140</v>
       </c>
-      <c r="B11" s="72" t="s">
+      <c r="B11" s="58" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="73">
+      <c r="C11" s="59">
         <v>38000</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B16" s="74" t="s">
+      <c r="B16" s="60" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="75">
+      <c r="C16" s="61">
         <f>SUMIF(Table2[Department],B6,Table2[Salary])</f>
         <v>58000</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B17" s="74" t="s">
+      <c r="B17" s="60" t="s">
         <v>13</v>
       </c>
-      <c r="C17" s="75">
+      <c r="C17" s="61">
         <f>SUMIF(Table2[Department],B7,Table2[Salary])</f>
         <v>95000</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B18" s="74" t="s">
+      <c r="B18" s="60" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="75">
+      <c r="C18" s="61">
         <f>SUMIF(Table2[Department],B9,Table2[Salary])</f>
         <v>80000</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B20" s="74" t="s">
+      <c r="B20" s="60" t="s">
         <v>141</v>
       </c>
-      <c r="C20" s="75">
+      <c r="C20" s="61">
         <f>AVERAGE(Table2[Salary])</f>
         <v>38833.333333333336</v>
       </c>
     </row>
     <row r="22" spans="2:3" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B22" s="74" t="s">
+      <c r="B22" s="60" t="s">
         <v>142</v>
       </c>
-      <c r="C22" s="74">
+      <c r="C22" s="60">
         <f>COUNTA(Table2[Employee Name])</f>
         <v>6</v>
       </c>
@@ -6096,165 +6082,165 @@
   </cols>
   <sheetData>
     <row r="5" spans="1:13" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="76" t="s">
+      <c r="A5" s="62" t="s">
         <v>78</v>
       </c>
-      <c r="B5" s="77" t="s">
+      <c r="B5" s="63" t="s">
         <v>143</v>
       </c>
-      <c r="C5" s="77" t="s">
+      <c r="C5" s="63" t="s">
         <v>144</v>
       </c>
-      <c r="D5" s="77" t="s">
+      <c r="D5" s="63" t="s">
         <v>145</v>
       </c>
-      <c r="E5" s="77" t="s">
+      <c r="E5" s="63" t="s">
         <v>146</v>
       </c>
-      <c r="F5" s="78" t="s">
+      <c r="F5" s="64" t="s">
         <v>147</v>
       </c>
-      <c r="G5" s="77" t="s">
+      <c r="G5" s="63" t="s">
         <v>148</v>
       </c>
-      <c r="H5" s="77" t="s">
+      <c r="H5" s="63" t="s">
         <v>149</v>
       </c>
-      <c r="K5" s="23" t="s">
+      <c r="K5" s="84" t="s">
         <v>150</v>
       </c>
-      <c r="L5" s="24"/>
-      <c r="M5" s="24"/>
+      <c r="L5" s="85"/>
+      <c r="M5" s="85"/>
     </row>
     <row r="6" spans="1:13" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="79" t="s">
+      <c r="A6" s="65" t="s">
         <v>85</v>
       </c>
-      <c r="B6" s="80" t="s">
+      <c r="B6" s="66" t="s">
         <v>151</v>
       </c>
-      <c r="C6" s="80" t="s">
+      <c r="C6" s="66" t="s">
         <v>152</v>
       </c>
-      <c r="D6" s="80" t="s">
+      <c r="D6" s="66" t="s">
         <v>151</v>
       </c>
-      <c r="E6" s="80" t="s">
+      <c r="E6" s="66" t="s">
         <v>151</v>
       </c>
-      <c r="F6" s="81" t="s">
+      <c r="F6" s="67" t="s">
         <v>151</v>
       </c>
-      <c r="G6" s="77">
+      <c r="G6" s="63">
         <f>COUNTIF(Table6[[#This Row],[Day 1]:[Day 5]],Table6[[#This Row],[Day 1]])</f>
         <v>4</v>
       </c>
-      <c r="H6" s="77">
+      <c r="H6" s="63">
         <f>COUNTIF(Table6[[#This Row],[Day 1]:[Present]],Table6[[#This Row],[Day 2]])</f>
         <v>1</v>
       </c>
-      <c r="K6" s="24"/>
-      <c r="L6" s="24"/>
-      <c r="M6" s="24"/>
+      <c r="K6" s="85"/>
+      <c r="L6" s="85"/>
+      <c r="M6" s="85"/>
     </row>
     <row r="7" spans="1:13" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="79" t="s">
+      <c r="A7" s="65" t="s">
         <v>86</v>
       </c>
-      <c r="B7" s="80" t="s">
+      <c r="B7" s="66" t="s">
         <v>151</v>
       </c>
-      <c r="C7" s="80" t="s">
+      <c r="C7" s="66" t="s">
         <v>151</v>
       </c>
-      <c r="D7" s="80" t="s">
+      <c r="D7" s="66" t="s">
         <v>151</v>
       </c>
-      <c r="E7" s="80" t="s">
+      <c r="E7" s="66" t="s">
         <v>152</v>
       </c>
-      <c r="F7" s="81" t="s">
+      <c r="F7" s="67" t="s">
         <v>151</v>
       </c>
-      <c r="G7" s="80">
+      <c r="G7" s="66">
         <f>COUNTIF(Table6[[#This Row],[Day 1]:[Day 5]],Table6[[#This Row],[Day 1]])</f>
         <v>4</v>
       </c>
-      <c r="H7" s="80">
+      <c r="H7" s="66">
         <f>COUNTIF(Table6[[#This Row],[Day 1]:[Present]],Table6[[#This Row],[Day 2]])</f>
         <v>4</v>
       </c>
-      <c r="K7" s="24"/>
-      <c r="L7" s="24"/>
-      <c r="M7" s="24"/>
+      <c r="K7" s="85"/>
+      <c r="L7" s="85"/>
+      <c r="M7" s="85"/>
     </row>
     <row r="8" spans="1:13" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="79" t="s">
+      <c r="A8" s="65" t="s">
         <v>87</v>
       </c>
-      <c r="B8" s="80" t="s">
+      <c r="B8" s="66" t="s">
         <v>152</v>
       </c>
-      <c r="C8" s="80" t="s">
+      <c r="C8" s="66" t="s">
         <v>151</v>
       </c>
-      <c r="D8" s="80" t="s">
+      <c r="D8" s="66" t="s">
         <v>151</v>
       </c>
-      <c r="E8" s="80" t="s">
+      <c r="E8" s="66" t="s">
         <v>151</v>
       </c>
-      <c r="F8" s="81" t="s">
+      <c r="F8" s="67" t="s">
         <v>151</v>
       </c>
-      <c r="G8" s="80">
+      <c r="G8" s="66">
         <f>COUNTIF(Table6[[#This Row],[Day 1]:[Day 5]],Table6[[#This Row],[Day 1]])</f>
         <v>1</v>
       </c>
-      <c r="H8" s="80">
+      <c r="H8" s="66">
         <f>COUNTIF(Table6[[#This Row],[Day 1]:[Present]],Table6[[#This Row],[Day 2]])</f>
         <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A9" s="82" t="s">
+      <c r="A9" s="68" t="s">
         <v>88</v>
       </c>
-      <c r="B9" s="83" t="s">
+      <c r="B9" s="69" t="s">
         <v>151</v>
       </c>
-      <c r="C9" s="83" t="s">
+      <c r="C9" s="69" t="s">
         <v>152</v>
       </c>
-      <c r="D9" s="83" t="s">
+      <c r="D9" s="69" t="s">
         <v>152</v>
       </c>
-      <c r="E9" s="83" t="s">
+      <c r="E9" s="69" t="s">
         <v>151</v>
       </c>
-      <c r="F9" s="84" t="s">
+      <c r="F9" s="70" t="s">
         <v>152</v>
       </c>
-      <c r="G9" s="83">
+      <c r="G9" s="69">
         <f>COUNTIF(Table6[[#This Row],[Day 1]:[Day 5]],Table6[[#This Row],[Day 1]])</f>
         <v>2</v>
       </c>
-      <c r="H9" s="83">
+      <c r="H9" s="69">
         <f>COUNTIF(Table6[[#This Row],[Day 1]:[Present]],Table6[[#This Row],[Day 2]])</f>
         <v>3</v>
       </c>
-      <c r="K9" s="85" t="s">
+      <c r="K9" s="92" t="s">
         <v>153</v>
       </c>
-      <c r="L9" s="85"/>
-      <c r="M9" s="85"/>
+      <c r="L9" s="92"/>
+      <c r="M9" s="92"/>
     </row>
     <row r="10" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="K10" s="85" t="s">
+      <c r="K10" s="92" t="s">
         <v>154</v>
       </c>
-      <c r="L10" s="85"/>
-      <c r="M10" s="85"/>
+      <c r="L10" s="92"/>
+      <c r="M10" s="92"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -6279,245 +6265,245 @@
   </cols>
   <sheetData>
     <row r="5" spans="1:15" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="86" t="s">
+      <c r="A5" s="71" t="s">
         <v>155</v>
       </c>
-      <c r="B5" s="87" t="s">
+      <c r="B5" s="72" t="s">
         <v>56</v>
       </c>
-      <c r="L5" s="88" t="s">
+      <c r="L5" s="93" t="s">
         <v>156</v>
       </c>
-      <c r="M5" s="89"/>
-      <c r="N5" s="89"/>
+      <c r="M5" s="94"/>
+      <c r="N5" s="94"/>
     </row>
     <row r="6" spans="1:15" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="90" t="s">
+      <c r="A6" s="73" t="s">
         <v>157</v>
       </c>
-      <c r="B6" s="91">
+      <c r="B6" s="74">
         <v>4500</v>
       </c>
-      <c r="L6" s="89"/>
-      <c r="M6" s="89"/>
-      <c r="N6" s="89"/>
+      <c r="L6" s="94"/>
+      <c r="M6" s="94"/>
+      <c r="N6" s="94"/>
     </row>
     <row r="7" spans="1:15" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="90" t="s">
+      <c r="A7" s="73" t="s">
         <v>158</v>
       </c>
-      <c r="B7" s="91">
+      <c r="B7" s="74">
         <v>12000</v>
       </c>
-      <c r="L7" s="89"/>
-      <c r="M7" s="89"/>
-      <c r="N7" s="89"/>
+      <c r="L7" s="94"/>
+      <c r="M7" s="94"/>
+      <c r="N7" s="94"/>
     </row>
     <row r="8" spans="1:15" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="90" t="s">
+      <c r="A8" s="73" t="s">
         <v>159</v>
       </c>
-      <c r="B8" s="91">
+      <c r="B8" s="74">
         <v>8000</v>
       </c>
     </row>
     <row r="9" spans="1:15" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="90" t="s">
+      <c r="A9" s="73" t="s">
         <v>160</v>
       </c>
-      <c r="B9" s="91">
+      <c r="B9" s="74">
         <v>25000</v>
       </c>
-      <c r="J9" s="92" t="s">
+      <c r="J9" s="95" t="s">
         <v>161</v>
       </c>
-      <c r="K9" s="92"/>
-      <c r="L9" s="92"/>
-      <c r="M9" s="92"/>
-      <c r="N9" s="92">
+      <c r="K9" s="95"/>
+      <c r="L9" s="95"/>
+      <c r="M9" s="95"/>
+      <c r="N9" s="95">
         <f>COUNTIF(Table7[Sales Amount],"&gt;10000")</f>
         <v>14</v>
       </c>
-      <c r="O9" s="92"/>
+      <c r="O9" s="95"/>
     </row>
     <row r="10" spans="1:15" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="90" t="s">
+      <c r="A10" s="73" t="s">
         <v>162</v>
       </c>
-      <c r="B10" s="91">
+      <c r="B10" s="74">
         <v>3000</v>
       </c>
-      <c r="J10" s="92"/>
-      <c r="K10" s="92"/>
-      <c r="L10" s="92"/>
-      <c r="M10" s="92"/>
-      <c r="N10" s="92"/>
-      <c r="O10" s="92"/>
+      <c r="J10" s="95"/>
+      <c r="K10" s="95"/>
+      <c r="L10" s="95"/>
+      <c r="M10" s="95"/>
+      <c r="N10" s="95"/>
+      <c r="O10" s="95"/>
     </row>
     <row r="11" spans="1:15" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="93" t="s">
+      <c r="A11" s="75" t="s">
         <v>163</v>
       </c>
-      <c r="B11" s="94">
+      <c r="B11" s="76">
         <v>15000</v>
       </c>
-      <c r="J11" s="22"/>
-      <c r="K11" s="22"/>
-      <c r="L11" s="22"/>
-      <c r="M11" s="22"/>
-      <c r="N11" s="22"/>
-      <c r="O11" s="22"/>
+      <c r="J11" s="16"/>
+      <c r="K11" s="16"/>
+      <c r="L11" s="16"/>
+      <c r="M11" s="16"/>
+      <c r="N11" s="16"/>
+      <c r="O11" s="16"/>
     </row>
     <row r="12" spans="1:15" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="90" t="s">
+      <c r="A12" s="73" t="s">
         <v>164</v>
       </c>
-      <c r="B12" s="91">
+      <c r="B12" s="74">
         <v>16889</v>
       </c>
-      <c r="J12" s="92" t="s">
+      <c r="J12" s="95" t="s">
         <v>165</v>
       </c>
-      <c r="K12" s="92"/>
-      <c r="L12" s="92"/>
-      <c r="M12" s="92"/>
-      <c r="N12" s="92">
+      <c r="K12" s="95"/>
+      <c r="L12" s="95"/>
+      <c r="M12" s="95"/>
+      <c r="N12" s="95">
         <f>COUNTIF(Table7[Sales Amount],"&lt;5000")</f>
         <v>3</v>
       </c>
-      <c r="O12" s="92"/>
+      <c r="O12" s="95"/>
     </row>
     <row r="13" spans="1:15" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="90" t="s">
+      <c r="A13" s="73" t="s">
         <v>166</v>
       </c>
-      <c r="B13" s="91">
+      <c r="B13" s="74">
         <v>17693</v>
       </c>
-      <c r="J13" s="92"/>
-      <c r="K13" s="92"/>
-      <c r="L13" s="92"/>
-      <c r="M13" s="92"/>
-      <c r="N13" s="92"/>
-      <c r="O13" s="92"/>
+      <c r="J13" s="95"/>
+      <c r="K13" s="95"/>
+      <c r="L13" s="95"/>
+      <c r="M13" s="95"/>
+      <c r="N13" s="95"/>
+      <c r="O13" s="95"/>
     </row>
     <row r="14" spans="1:15" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="90" t="s">
+      <c r="A14" s="73" t="s">
         <v>167</v>
       </c>
-      <c r="B14" s="91">
+      <c r="B14" s="74">
         <v>12972</v>
       </c>
     </row>
     <row r="15" spans="1:15" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="90" t="s">
+      <c r="A15" s="73" t="s">
         <v>168</v>
       </c>
-      <c r="B15" s="91">
+      <c r="B15" s="74">
         <v>5059</v>
       </c>
     </row>
     <row r="16" spans="1:15" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="90" t="s">
+      <c r="A16" s="73" t="s">
         <v>169</v>
       </c>
-      <c r="B16" s="91">
+      <c r="B16" s="74">
         <v>12671</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="93" t="s">
+      <c r="A17" s="75" t="s">
         <v>170</v>
       </c>
-      <c r="B17" s="91">
+      <c r="B17" s="74">
         <v>17613</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="90" t="s">
+      <c r="A18" s="73" t="s">
         <v>171</v>
       </c>
-      <c r="B18" s="91">
+      <c r="B18" s="74">
         <v>19518</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="90" t="s">
+      <c r="A19" s="73" t="s">
         <v>172</v>
       </c>
-      <c r="B19" s="91">
+      <c r="B19" s="74">
         <v>17721</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="90" t="s">
+      <c r="A20" s="73" t="s">
         <v>173</v>
       </c>
-      <c r="B20" s="91">
+      <c r="B20" s="74">
         <v>16599</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="90" t="s">
+      <c r="A21" s="73" t="s">
         <v>174</v>
       </c>
-      <c r="B21" s="91">
+      <c r="B21" s="74">
         <v>14952</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="90" t="s">
+      <c r="A22" s="73" t="s">
         <v>175</v>
       </c>
-      <c r="B22" s="91">
+      <c r="B22" s="74">
         <v>9678</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="93" t="s">
+      <c r="A23" s="75" t="s">
         <v>176</v>
       </c>
-      <c r="B23" s="91">
+      <c r="B23" s="74">
         <v>9739</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="90" t="s">
+      <c r="A24" s="73" t="s">
         <v>177</v>
       </c>
-      <c r="B24" s="91">
+      <c r="B24" s="74">
         <v>10543</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="90" t="s">
+      <c r="A25" s="73" t="s">
         <v>178</v>
       </c>
-      <c r="B25" s="91">
+      <c r="B25" s="74">
         <v>15534</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="90" t="s">
+      <c r="A26" s="73" t="s">
         <v>179</v>
       </c>
-      <c r="B26" s="91">
+      <c r="B26" s="74">
         <v>5135</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="90" t="s">
+      <c r="A27" s="73" t="s">
         <v>180</v>
       </c>
-      <c r="B27" s="91">
+      <c r="B27" s="74">
         <v>9395</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="90" t="s">
+      <c r="A28" s="73" t="s">
         <v>181</v>
       </c>
-      <c r="B28" s="91">
+      <c r="B28" s="74">
         <v>2265</v>
       </c>
     </row>
@@ -6546,72 +6532,72 @@
   </cols>
   <sheetData>
     <row r="5" spans="1:13" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="76" t="s">
+      <c r="A5" s="62" t="s">
         <v>182</v>
       </c>
-      <c r="B5" s="78" t="s">
+      <c r="B5" s="64" t="s">
         <v>56</v>
       </c>
-      <c r="J5" s="23" t="s">
+      <c r="J5" s="84" t="s">
         <v>183</v>
       </c>
-      <c r="K5" s="24"/>
-      <c r="L5" s="24"/>
-      <c r="M5" s="24"/>
+      <c r="K5" s="85"/>
+      <c r="L5" s="85"/>
+      <c r="M5" s="85"/>
     </row>
     <row r="6" spans="1:13" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="79" t="s">
+      <c r="A6" s="65" t="s">
         <v>184</v>
       </c>
-      <c r="B6" s="81">
+      <c r="B6" s="67">
         <v>22000</v>
       </c>
-      <c r="J6" s="24"/>
-      <c r="K6" s="24"/>
-      <c r="L6" s="24"/>
-      <c r="M6" s="24"/>
+      <c r="J6" s="85"/>
+      <c r="K6" s="85"/>
+      <c r="L6" s="85"/>
+      <c r="M6" s="85"/>
     </row>
     <row r="7" spans="1:13" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="79" t="s">
+      <c r="A7" s="65" t="s">
         <v>185</v>
       </c>
-      <c r="B7" s="81">
+      <c r="B7" s="67">
         <v>3500</v>
       </c>
-      <c r="J7" s="24"/>
-      <c r="K7" s="24"/>
-      <c r="L7" s="24"/>
-      <c r="M7" s="24"/>
+      <c r="J7" s="85"/>
+      <c r="K7" s="85"/>
+      <c r="L7" s="85"/>
+      <c r="M7" s="85"/>
     </row>
     <row r="8" spans="1:13" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="79" t="s">
+      <c r="A8" s="65" t="s">
         <v>186</v>
       </c>
-      <c r="B8" s="81">
+      <c r="B8" s="67">
         <v>58000</v>
       </c>
-      <c r="J8" s="24"/>
-      <c r="K8" s="24"/>
-      <c r="L8" s="24"/>
-      <c r="M8" s="24"/>
+      <c r="J8" s="85"/>
+      <c r="K8" s="85"/>
+      <c r="L8" s="85"/>
+      <c r="M8" s="85"/>
     </row>
     <row r="9" spans="1:13" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="79" t="s">
+      <c r="A9" s="65" t="s">
         <v>187</v>
       </c>
-      <c r="B9" s="81">
+      <c r="B9" s="67">
         <v>1800</v>
       </c>
-      <c r="J9" s="24"/>
-      <c r="K9" s="24"/>
-      <c r="L9" s="24"/>
-      <c r="M9" s="24"/>
+      <c r="J9" s="85"/>
+      <c r="K9" s="85"/>
+      <c r="L9" s="85"/>
+      <c r="M9" s="85"/>
     </row>
     <row r="10" spans="1:13" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A10" s="82" t="s">
+      <c r="A10" s="68" t="s">
         <v>188</v>
       </c>
-      <c r="B10" s="84">
+      <c r="B10" s="70">
         <v>12000</v>
       </c>
     </row>
@@ -6620,10 +6606,10 @@
     <mergeCell ref="J5:M9"/>
   </mergeCells>
   <conditionalFormatting sqref="B6:B10">
-    <cfRule type="cellIs" dxfId="29" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="28" priority="1" operator="lessThan">
       <formula>5000</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="30" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="27" priority="2" operator="greaterThan">
       <formula>20000</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6636,7 +6622,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA6D751A-D27F-44D3-BC95-FB75FD6E58BF}">
-  <dimension ref="A5:N14"/>
+  <dimension ref="A5:N16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.5703125" customWidth="1"/>
@@ -6645,109 +6631,114 @@
   </cols>
   <sheetData>
     <row r="5" spans="1:14" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="76" t="s">
+      <c r="A5" s="62" t="s">
         <v>77</v>
       </c>
-      <c r="B5" s="77" t="s">
+      <c r="B5" s="63" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="78" t="s">
+      <c r="C5" s="64" t="s">
         <v>189</v>
       </c>
-      <c r="K5" s="23" t="s">
+      <c r="K5" s="84" t="s">
         <v>190</v>
       </c>
-      <c r="L5" s="24"/>
-      <c r="M5" s="24"/>
-      <c r="N5" s="24"/>
+      <c r="L5" s="85"/>
+      <c r="M5" s="85"/>
+      <c r="N5" s="85"/>
     </row>
     <row r="6" spans="1:14" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="79">
+      <c r="A6" s="65">
         <v>1</v>
       </c>
-      <c r="B6" s="80" t="s">
+      <c r="B6" s="66" t="s">
         <v>139</v>
       </c>
-      <c r="C6" s="81">
+      <c r="C6" s="67">
         <v>85</v>
       </c>
-      <c r="K6" s="24"/>
-      <c r="L6" s="24"/>
-      <c r="M6" s="24"/>
-      <c r="N6" s="24"/>
+      <c r="K6" s="85"/>
+      <c r="L6" s="85"/>
+      <c r="M6" s="85"/>
+      <c r="N6" s="85"/>
     </row>
     <row r="7" spans="1:14" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="79">
+      <c r="A7" s="65">
         <v>2</v>
       </c>
-      <c r="B7" s="80" t="s">
+      <c r="B7" s="66" t="s">
         <v>191</v>
       </c>
-      <c r="C7" s="81">
+      <c r="C7" s="67">
         <v>72</v>
       </c>
-      <c r="K7" s="24"/>
-      <c r="L7" s="24"/>
-      <c r="M7" s="24"/>
-      <c r="N7" s="24"/>
+      <c r="K7" s="85"/>
+      <c r="L7" s="85"/>
+      <c r="M7" s="85"/>
+      <c r="N7" s="85"/>
     </row>
     <row r="8" spans="1:14" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="79">
+      <c r="A8" s="65">
         <v>3</v>
       </c>
-      <c r="B8" s="80" t="s">
+      <c r="B8" s="66" t="s">
         <v>192</v>
       </c>
-      <c r="C8" s="81">
+      <c r="C8" s="67">
         <v>39</v>
       </c>
-      <c r="K8" s="24"/>
-      <c r="L8" s="24"/>
-      <c r="M8" s="24"/>
-      <c r="N8" s="24"/>
+      <c r="K8" s="85"/>
+      <c r="L8" s="85"/>
+      <c r="M8" s="85"/>
+      <c r="N8" s="85"/>
     </row>
     <row r="9" spans="1:14" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="79">
+      <c r="A9" s="65">
         <v>4</v>
       </c>
-      <c r="B9" s="80" t="s">
+      <c r="B9" s="66" t="s">
         <v>193</v>
       </c>
-      <c r="C9" s="81">
+      <c r="C9" s="67">
         <v>91</v>
       </c>
-      <c r="K9" s="24"/>
-      <c r="L9" s="24"/>
-      <c r="M9" s="24"/>
-      <c r="N9" s="24"/>
+      <c r="K9" s="85"/>
+      <c r="L9" s="85"/>
+      <c r="M9" s="85"/>
+      <c r="N9" s="85"/>
     </row>
     <row r="10" spans="1:14" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A10" s="82">
+      <c r="A10" s="68">
         <v>5</v>
       </c>
-      <c r="B10" s="83" t="s">
+      <c r="B10" s="69" t="s">
         <v>194</v>
       </c>
-      <c r="C10" s="84">
+      <c r="C10" s="70">
         <v>28</v>
       </c>
-      <c r="K10" s="24"/>
-      <c r="L10" s="24"/>
-      <c r="M10" s="24"/>
-      <c r="N10" s="24"/>
+      <c r="K10" s="85"/>
+      <c r="L10" s="85"/>
+      <c r="M10" s="85"/>
+      <c r="N10" s="85"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="M14" s="95"/>
+      <c r="M14" s="77"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M16" t="s">
+        <v>201</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="K5:N10"/>
   </mergeCells>
   <conditionalFormatting sqref="C6:C10">
-    <cfRule type="cellIs" dxfId="8" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="19" priority="1" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="2" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="18" priority="2" operator="greaterThanOrEqual">
       <formula>75</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Practical Task/01_Practical_task.xlsx
+++ b/Practical Task/01_Practical_task.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASDC11\Desktop\Smit\Data_Analytics\Practical Task\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A66B8F7-DC97-4C8F-8069-3F8929237DF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{710DDED3-EA3D-4FA0-A0EF-D1547A4F61C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="5" activeTab="8" xr2:uid="{B7CA3347-B884-4512-82BB-7C62A0B069B5}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="203">
   <si>
     <t>24/01/2026</t>
   </si>
@@ -668,6 +668,9 @@
   </si>
   <si>
     <t>ss</t>
+  </si>
+  <si>
+    <t>sss</t>
   </si>
 </sst>
 </file>
@@ -6726,6 +6729,9 @@
       <c r="M14" s="77"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="J16" t="s">
+        <v>202</v>
+      </c>
       <c r="M16" t="s">
         <v>201</v>
       </c>

--- a/Practical Task/01_Practical_task.xlsx
+++ b/Practical Task/01_Practical_task.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASDC11\Desktop\Smit\Data_Analytics\Practical Task\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{710DDED3-EA3D-4FA0-A0EF-D1547A4F61C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAF1B52A-068C-4FD4-BC73-0881FFA49EB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="5" activeTab="8" xr2:uid="{B7CA3347-B884-4512-82BB-7C62A0B069B5}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="201">
   <si>
     <t>24/01/2026</t>
   </si>
@@ -665,12 +665,6 @@
   </si>
   <si>
     <t>Mohan</t>
-  </si>
-  <si>
-    <t>ss</t>
-  </si>
-  <si>
-    <t>sss</t>
   </si>
 </sst>
 </file>
@@ -6625,7 +6619,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA6D751A-D27F-44D3-BC95-FB75FD6E58BF}">
-  <dimension ref="A5:N16"/>
+  <dimension ref="A5:N14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.5703125" customWidth="1"/>
@@ -6727,14 +6721,6 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="M14" s="77"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="J16" t="s">
-        <v>202</v>
-      </c>
-      <c r="M16" t="s">
-        <v>201</v>
-      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
